--- a/codice/Polline_Template_Settimanale.xlsx
+++ b/codice/Polline_Template_Settimanale.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="DD-MM-YYYY"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -129,8 +129,31 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Cambria"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -226,8 +249,18 @@
         <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -305,6 +338,64 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -316,7 +407,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -577,6 +668,276 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -587,7 +948,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -613,6 +974,20 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF8C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1655,81 +2030,81 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="40">
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="165" t="inlineStr">
         <is>
           <t>POLLINI</t>
         </is>
       </c>
-      <c r="E5" s="46" t="n"/>
-      <c r="F5" s="47" t="n"/>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="E5" s="166" t="n"/>
+      <c r="F5" s="166" t="n"/>
+      <c r="G5" s="165" t="inlineStr">
         <is>
           <t>LUNEDI</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="165" t="inlineStr">
         <is>
           <t>MARTEDI</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="165" t="inlineStr">
         <is>
           <t>MERC.</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="165" t="inlineStr">
         <is>
           <t>GIOVEDI</t>
         </is>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="165" t="inlineStr">
         <is>
           <t>VENERDI</t>
         </is>
       </c>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="L5" s="165" t="inlineStr">
         <is>
           <t>SABATO</t>
         </is>
       </c>
-      <c r="M5" s="45" t="inlineStr">
+      <c r="M5" s="165" t="inlineStr">
         <is>
           <t>DOMEN.</t>
         </is>
       </c>
-      <c r="P5" s="48" t="inlineStr">
+      <c r="P5" s="167" t="inlineStr">
         <is>
           <t>POLLINI</t>
         </is>
       </c>
-      <c r="Q5" s="46" t="n"/>
-      <c r="R5" s="47" t="n"/>
-      <c r="S5" s="45" t="inlineStr">
+      <c r="Q5" s="166" t="n"/>
+      <c r="R5" s="166" t="n"/>
+      <c r="S5" s="165" t="inlineStr">
         <is>
           <t>LUNEDI</t>
         </is>
       </c>
-      <c r="T5" s="45" t="inlineStr">
+      <c r="T5" s="165" t="inlineStr">
         <is>
           <t>MARTEDI</t>
         </is>
       </c>
-      <c r="U5" s="45" t="inlineStr">
+      <c r="U5" s="165" t="inlineStr">
         <is>
           <t>MERC.</t>
         </is>
       </c>
-      <c r="V5" s="45" t="inlineStr">
+      <c r="V5" s="165" t="inlineStr">
         <is>
           <t>GIOVEDI</t>
         </is>
       </c>
-      <c r="W5" s="45" t="inlineStr">
+      <c r="W5" s="165" t="inlineStr">
         <is>
           <t>VENERDI</t>
         </is>
       </c>
-      <c r="X5" s="45" t="inlineStr">
+      <c r="X5" s="165" t="inlineStr">
         <is>
           <t>SABATO</t>
         </is>
@@ -1746,48 +2121,48 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="40">
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="168" t="inlineStr">
         <is>
           <t>ACERACEAE</t>
         </is>
       </c>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="47" t="n"/>
-      <c r="G6" s="52" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="53" t="n"/>
-      <c r="M6" s="53" t="n"/>
-      <c r="P6" s="54" t="inlineStr">
+      <c r="E6" s="169" t="n"/>
+      <c r="F6" s="169" t="n"/>
+      <c r="G6" s="170" t="n"/>
+      <c r="H6" s="171" t="n"/>
+      <c r="I6" s="171" t="n"/>
+      <c r="J6" s="171" t="n"/>
+      <c r="K6" s="171" t="n"/>
+      <c r="L6" s="171" t="n"/>
+      <c r="M6" s="171" t="n"/>
+      <c r="P6" s="172" t="inlineStr">
         <is>
           <t>ACERACEAE</t>
         </is>
       </c>
-      <c r="Q6" s="46" t="n"/>
-      <c r="R6" s="47" t="n"/>
-      <c r="S6" s="55">
+      <c r="Q6" s="169" t="n"/>
+      <c r="R6" s="169" t="n"/>
+      <c r="S6" s="173">
         <f>G6*$Q$3</f>
         <v/>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="173">
         <f>H6*$Q$3</f>
         <v/>
       </c>
-      <c r="U6" s="55">
+      <c r="U6" s="173">
         <f>I6*$Q$3</f>
         <v/>
       </c>
-      <c r="V6" s="55">
+      <c r="V6" s="173">
         <f>J6*$Q$3</f>
         <v/>
       </c>
-      <c r="W6" s="55">
+      <c r="W6" s="173">
         <f>K6*$Q$3</f>
         <v/>
       </c>
-      <c r="X6" s="55">
+      <c r="X6" s="173">
         <f>L6*$Q$3</f>
         <v/>
       </c>
@@ -1801,48 +2176,48 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="40">
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="174" t="inlineStr">
         <is>
           <t>ALTRI POLLINI</t>
         </is>
       </c>
-      <c r="E7" s="46" t="n"/>
-      <c r="F7" s="47" t="n"/>
-      <c r="G7" s="53" t="n"/>
-      <c r="H7" s="53" t="n"/>
-      <c r="I7" s="53" t="n"/>
-      <c r="J7" s="53" t="n"/>
-      <c r="K7" s="53" t="n"/>
-      <c r="L7" s="53" t="n"/>
-      <c r="M7" s="53" t="n"/>
-      <c r="P7" s="59" t="inlineStr">
+      <c r="E7" s="169" t="n"/>
+      <c r="F7" s="169" t="n"/>
+      <c r="G7" s="171" t="n"/>
+      <c r="H7" s="171" t="n"/>
+      <c r="I7" s="171" t="n"/>
+      <c r="J7" s="171" t="n"/>
+      <c r="K7" s="171" t="n"/>
+      <c r="L7" s="171" t="n"/>
+      <c r="M7" s="171" t="n"/>
+      <c r="P7" s="166" t="inlineStr">
         <is>
           <t>ALTRI POLLINI</t>
         </is>
       </c>
-      <c r="Q7" s="46" t="n"/>
-      <c r="R7" s="47" t="n"/>
-      <c r="S7" s="55">
+      <c r="Q7" s="169" t="n"/>
+      <c r="R7" s="169" t="n"/>
+      <c r="S7" s="173">
         <f>G7*$Q$3</f>
         <v/>
       </c>
-      <c r="T7" s="55">
+      <c r="T7" s="173">
         <f>H7*$Q$3</f>
         <v/>
       </c>
-      <c r="U7" s="55">
+      <c r="U7" s="173">
         <f>I7*$Q$3</f>
         <v/>
       </c>
-      <c r="V7" s="55">
+      <c r="V7" s="173">
         <f>J7*$Q$3</f>
         <v/>
       </c>
-      <c r="W7" s="55">
+      <c r="W7" s="173">
         <f>K7*$Q$3</f>
         <v/>
       </c>
-      <c r="X7" s="55">
+      <c r="X7" s="173">
         <f>L7*$Q$3</f>
         <v/>
       </c>
@@ -1856,48 +2231,48 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="40">
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="174" t="inlineStr">
         <is>
           <t>BETULACEAE</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
-      <c r="F8" s="47" t="n"/>
-      <c r="G8" s="53" t="n"/>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="53" t="n"/>
-      <c r="K8" s="53" t="n"/>
-      <c r="L8" s="53" t="n"/>
-      <c r="M8" s="53" t="n"/>
-      <c r="P8" s="59" t="inlineStr">
+      <c r="E8" s="169" t="n"/>
+      <c r="F8" s="169" t="n"/>
+      <c r="G8" s="171" t="n"/>
+      <c r="H8" s="170" t="n"/>
+      <c r="I8" s="171" t="n"/>
+      <c r="J8" s="171" t="n"/>
+      <c r="K8" s="171" t="n"/>
+      <c r="L8" s="171" t="n"/>
+      <c r="M8" s="171" t="n"/>
+      <c r="P8" s="166" t="inlineStr">
         <is>
           <t>BETULACEAE</t>
         </is>
       </c>
-      <c r="Q8" s="46" t="n"/>
-      <c r="R8" s="47" t="n"/>
-      <c r="S8" s="55">
+      <c r="Q8" s="169" t="n"/>
+      <c r="R8" s="169" t="n"/>
+      <c r="S8" s="173">
         <f>G8*$Q$3</f>
         <v/>
       </c>
-      <c r="T8" s="55">
+      <c r="T8" s="173">
         <f>H8*$Q$3</f>
         <v/>
       </c>
-      <c r="U8" s="55">
+      <c r="U8" s="173">
         <f>I8*$Q$3</f>
         <v/>
       </c>
-      <c r="V8" s="55">
+      <c r="V8" s="173">
         <f>J8*$Q$3</f>
         <v/>
       </c>
-      <c r="W8" s="55">
+      <c r="W8" s="173">
         <f>K8*$Q$3</f>
         <v/>
       </c>
-      <c r="X8" s="55">
+      <c r="X8" s="173">
         <f>L8*$Q$3</f>
         <v/>
       </c>
@@ -1911,48 +2286,48 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="40">
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="174" t="inlineStr">
         <is>
           <t>Alnus</t>
         </is>
       </c>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="47" t="n"/>
-      <c r="G9" s="53" t="n"/>
-      <c r="H9" s="53" t="n"/>
-      <c r="I9" s="53" t="n"/>
-      <c r="J9" s="53" t="n"/>
-      <c r="K9" s="52" t="n"/>
-      <c r="L9" s="53" t="n"/>
-      <c r="M9" s="53" t="n"/>
-      <c r="P9" s="59" t="inlineStr">
+      <c r="E9" s="169" t="n"/>
+      <c r="F9" s="169" t="n"/>
+      <c r="G9" s="171" t="n"/>
+      <c r="H9" s="171" t="n"/>
+      <c r="I9" s="171" t="n"/>
+      <c r="J9" s="171" t="n"/>
+      <c r="K9" s="170" t="n"/>
+      <c r="L9" s="171" t="n"/>
+      <c r="M9" s="171" t="n"/>
+      <c r="P9" s="166" t="inlineStr">
         <is>
           <t>Alnus</t>
         </is>
       </c>
-      <c r="Q9" s="46" t="n"/>
-      <c r="R9" s="47" t="n"/>
-      <c r="S9" s="55">
+      <c r="Q9" s="169" t="n"/>
+      <c r="R9" s="169" t="n"/>
+      <c r="S9" s="173">
         <f>G9*$Q$3</f>
         <v/>
       </c>
-      <c r="T9" s="55">
+      <c r="T9" s="173">
         <f>H9*$Q$3</f>
         <v/>
       </c>
-      <c r="U9" s="55">
+      <c r="U9" s="173">
         <f>I9*$Q$3</f>
         <v/>
       </c>
-      <c r="V9" s="55">
+      <c r="V9" s="173">
         <f>J9*$Q$3</f>
         <v/>
       </c>
-      <c r="W9" s="55">
+      <c r="W9" s="173">
         <f>K9*$Q$3</f>
         <v/>
       </c>
-      <c r="X9" s="55">
+      <c r="X9" s="173">
         <f>L9*$Q$3</f>
         <v/>
       </c>
@@ -1966,48 +2341,48 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="40">
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="175" t="inlineStr">
         <is>
           <t>Betula</t>
         </is>
       </c>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="47" t="n"/>
-      <c r="G10" s="61" t="n"/>
-      <c r="H10" s="61" t="n"/>
-      <c r="I10" s="61" t="n"/>
-      <c r="J10" s="61" t="n"/>
-      <c r="K10" s="61" t="n"/>
-      <c r="L10" s="61" t="n"/>
-      <c r="M10" s="61" t="n"/>
-      <c r="P10" s="62" t="inlineStr">
+      <c r="E10" s="169" t="n"/>
+      <c r="F10" s="169" t="n"/>
+      <c r="G10" s="176" t="n"/>
+      <c r="H10" s="176" t="n"/>
+      <c r="I10" s="176" t="n"/>
+      <c r="J10" s="176" t="n"/>
+      <c r="K10" s="176" t="n"/>
+      <c r="L10" s="176" t="n"/>
+      <c r="M10" s="176" t="n"/>
+      <c r="P10" s="177" t="inlineStr">
         <is>
           <t>Betula</t>
         </is>
       </c>
-      <c r="Q10" s="46" t="n"/>
-      <c r="R10" s="47" t="n"/>
-      <c r="S10" s="63">
+      <c r="Q10" s="169" t="n"/>
+      <c r="R10" s="169" t="n"/>
+      <c r="S10" s="178">
         <f>G10*$Q$3</f>
         <v/>
       </c>
-      <c r="T10" s="63">
+      <c r="T10" s="178">
         <f>H10*$Q$3</f>
         <v/>
       </c>
-      <c r="U10" s="63">
+      <c r="U10" s="178">
         <f>I10*$Q$3</f>
         <v/>
       </c>
-      <c r="V10" s="63">
+      <c r="V10" s="178">
         <f>J10*$Q$3</f>
         <v/>
       </c>
-      <c r="W10" s="63">
+      <c r="W10" s="178">
         <f>K10*$Q$3</f>
         <v/>
       </c>
-      <c r="X10" s="63">
+      <c r="X10" s="178">
         <f>L10*$Q$3</f>
         <v/>
       </c>
@@ -2021,48 +2396,48 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="40">
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="168" t="inlineStr">
         <is>
           <t>CANNABACEAE</t>
         </is>
       </c>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="47" t="n"/>
-      <c r="G11" s="53" t="n"/>
-      <c r="H11" s="53" t="n"/>
-      <c r="I11" s="53" t="n"/>
-      <c r="J11" s="53" t="n"/>
-      <c r="K11" s="53" t="n"/>
-      <c r="L11" s="53" t="n"/>
-      <c r="M11" s="53" t="n"/>
-      <c r="P11" s="54" t="inlineStr">
+      <c r="E11" s="169" t="n"/>
+      <c r="F11" s="169" t="n"/>
+      <c r="G11" s="171" t="n"/>
+      <c r="H11" s="171" t="n"/>
+      <c r="I11" s="171" t="n"/>
+      <c r="J11" s="171" t="n"/>
+      <c r="K11" s="171" t="n"/>
+      <c r="L11" s="171" t="n"/>
+      <c r="M11" s="171" t="n"/>
+      <c r="P11" s="172" t="inlineStr">
         <is>
           <t>CANNABACEAE</t>
         </is>
       </c>
-      <c r="Q11" s="46" t="n"/>
-      <c r="R11" s="47" t="n"/>
-      <c r="S11" s="55">
+      <c r="Q11" s="169" t="n"/>
+      <c r="R11" s="169" t="n"/>
+      <c r="S11" s="173">
         <f>G11*$Q$3</f>
         <v/>
       </c>
-      <c r="T11" s="55">
+      <c r="T11" s="173">
         <f>H11*$Q$3</f>
         <v/>
       </c>
-      <c r="U11" s="55">
+      <c r="U11" s="173">
         <f>I11*$Q$3</f>
         <v/>
       </c>
-      <c r="V11" s="55">
+      <c r="V11" s="173">
         <f>J11*$Q$3</f>
         <v/>
       </c>
-      <c r="W11" s="55">
+      <c r="W11" s="173">
         <f>K11*$Q$3</f>
         <v/>
       </c>
-      <c r="X11" s="55">
+      <c r="X11" s="173">
         <f>L11*$Q$3</f>
         <v/>
       </c>
@@ -2076,48 +2451,48 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="40">
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="174" t="inlineStr">
         <is>
           <t>CHENO-AMAR</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="53" t="n"/>
-      <c r="H12" s="53" t="n"/>
-      <c r="I12" s="53" t="n"/>
-      <c r="J12" s="53" t="n"/>
-      <c r="K12" s="53" t="n"/>
-      <c r="L12" s="53" t="n"/>
-      <c r="M12" s="53" t="n"/>
-      <c r="P12" s="59" t="inlineStr">
+      <c r="E12" s="169" t="n"/>
+      <c r="F12" s="169" t="n"/>
+      <c r="G12" s="171" t="n"/>
+      <c r="H12" s="171" t="n"/>
+      <c r="I12" s="171" t="n"/>
+      <c r="J12" s="171" t="n"/>
+      <c r="K12" s="171" t="n"/>
+      <c r="L12" s="171" t="n"/>
+      <c r="M12" s="171" t="n"/>
+      <c r="P12" s="166" t="inlineStr">
         <is>
           <t>CHENO-AMAR</t>
         </is>
       </c>
-      <c r="Q12" s="46" t="n"/>
-      <c r="R12" s="47" t="n"/>
-      <c r="S12" s="55">
+      <c r="Q12" s="169" t="n"/>
+      <c r="R12" s="169" t="n"/>
+      <c r="S12" s="173">
         <f>G12*$Q$3</f>
         <v/>
       </c>
-      <c r="T12" s="55">
+      <c r="T12" s="173">
         <f>H12*$Q$3</f>
         <v/>
       </c>
-      <c r="U12" s="55">
+      <c r="U12" s="173">
         <f>I12*$Q$3</f>
         <v/>
       </c>
-      <c r="V12" s="55">
+      <c r="V12" s="173">
         <f>J12*$Q$3</f>
         <v/>
       </c>
-      <c r="W12" s="55">
+      <c r="W12" s="173">
         <f>K12*$Q$3</f>
         <v/>
       </c>
-      <c r="X12" s="55">
+      <c r="X12" s="173">
         <f>L12*$Q$3</f>
         <v/>
       </c>
@@ -2131,48 +2506,48 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="40">
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="174" t="inlineStr">
         <is>
           <t>COMPOSITAE</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="47" t="n"/>
-      <c r="G13" s="53" t="n"/>
-      <c r="H13" s="53" t="n"/>
-      <c r="I13" s="53" t="n"/>
-      <c r="J13" s="53" t="n"/>
-      <c r="K13" s="53" t="n"/>
-      <c r="L13" s="53" t="n"/>
-      <c r="M13" s="53" t="n"/>
-      <c r="P13" s="59" t="inlineStr">
+      <c r="E13" s="169" t="n"/>
+      <c r="F13" s="169" t="n"/>
+      <c r="G13" s="171" t="n"/>
+      <c r="H13" s="171" t="n"/>
+      <c r="I13" s="171" t="n"/>
+      <c r="J13" s="171" t="n"/>
+      <c r="K13" s="171" t="n"/>
+      <c r="L13" s="171" t="n"/>
+      <c r="M13" s="171" t="n"/>
+      <c r="P13" s="166" t="inlineStr">
         <is>
           <t>COMPOSITAE</t>
         </is>
       </c>
-      <c r="Q13" s="46" t="n"/>
-      <c r="R13" s="47" t="n"/>
-      <c r="S13" s="55">
+      <c r="Q13" s="169" t="n"/>
+      <c r="R13" s="169" t="n"/>
+      <c r="S13" s="173">
         <f>G13*$Q$3</f>
         <v/>
       </c>
-      <c r="T13" s="55">
+      <c r="T13" s="173">
         <f>H13*$Q$3</f>
         <v/>
       </c>
-      <c r="U13" s="55">
+      <c r="U13" s="173">
         <f>I13*$Q$3</f>
         <v/>
       </c>
-      <c r="V13" s="55">
+      <c r="V13" s="173">
         <f>J13*$Q$3</f>
         <v/>
       </c>
-      <c r="W13" s="55">
+      <c r="W13" s="173">
         <f>K13*$Q$3</f>
         <v/>
       </c>
-      <c r="X13" s="55">
+      <c r="X13" s="173">
         <f>L13*$Q$3</f>
         <v/>
       </c>
@@ -2186,48 +2561,48 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="40">
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="174" t="inlineStr">
         <is>
           <t>Altre compositae</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="47" t="n"/>
-      <c r="G14" s="53" t="n"/>
-      <c r="H14" s="53" t="n"/>
-      <c r="I14" s="53" t="n"/>
-      <c r="J14" s="53" t="n"/>
-      <c r="K14" s="53" t="n"/>
-      <c r="L14" s="53" t="n"/>
-      <c r="M14" s="53" t="n"/>
-      <c r="P14" s="59" t="inlineStr">
+      <c r="E14" s="169" t="n"/>
+      <c r="F14" s="169" t="n"/>
+      <c r="G14" s="171" t="n"/>
+      <c r="H14" s="171" t="n"/>
+      <c r="I14" s="171" t="n"/>
+      <c r="J14" s="171" t="n"/>
+      <c r="K14" s="171" t="n"/>
+      <c r="L14" s="171" t="n"/>
+      <c r="M14" s="171" t="n"/>
+      <c r="P14" s="166" t="inlineStr">
         <is>
           <t>Altre compositae</t>
         </is>
       </c>
-      <c r="Q14" s="46" t="n"/>
-      <c r="R14" s="47" t="n"/>
-      <c r="S14" s="55">
+      <c r="Q14" s="169" t="n"/>
+      <c r="R14" s="169" t="n"/>
+      <c r="S14" s="173">
         <f>G14*$Q$3</f>
         <v/>
       </c>
-      <c r="T14" s="55">
+      <c r="T14" s="173">
         <f>H14*$Q$3</f>
         <v/>
       </c>
-      <c r="U14" s="55">
+      <c r="U14" s="173">
         <f>I14*$Q$3</f>
         <v/>
       </c>
-      <c r="V14" s="55">
+      <c r="V14" s="173">
         <f>J14*$Q$3</f>
         <v/>
       </c>
-      <c r="W14" s="55">
+      <c r="W14" s="173">
         <f>K14*$Q$3</f>
         <v/>
       </c>
-      <c r="X14" s="55">
+      <c r="X14" s="173">
         <f>L14*$Q$3</f>
         <v/>
       </c>
@@ -2241,48 +2616,48 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="40">
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="174" t="inlineStr">
         <is>
           <t>Ambrosia</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="47" t="n"/>
-      <c r="G15" s="53" t="n"/>
-      <c r="H15" s="53" t="n"/>
-      <c r="I15" s="53" t="n"/>
-      <c r="J15" s="53" t="n"/>
-      <c r="K15" s="53" t="n"/>
-      <c r="L15" s="53" t="n"/>
-      <c r="M15" s="53" t="n"/>
-      <c r="P15" s="59" t="inlineStr">
+      <c r="E15" s="169" t="n"/>
+      <c r="F15" s="169" t="n"/>
+      <c r="G15" s="171" t="n"/>
+      <c r="H15" s="171" t="n"/>
+      <c r="I15" s="171" t="n"/>
+      <c r="J15" s="171" t="n"/>
+      <c r="K15" s="171" t="n"/>
+      <c r="L15" s="171" t="n"/>
+      <c r="M15" s="171" t="n"/>
+      <c r="P15" s="166" t="inlineStr">
         <is>
           <t>Ambrosia</t>
         </is>
       </c>
-      <c r="Q15" s="46" t="n"/>
-      <c r="R15" s="47" t="n"/>
-      <c r="S15" s="55">
+      <c r="Q15" s="169" t="n"/>
+      <c r="R15" s="169" t="n"/>
+      <c r="S15" s="173">
         <f>G15*$Q$3</f>
         <v/>
       </c>
-      <c r="T15" s="55">
+      <c r="T15" s="173">
         <f>H15*$Q$3</f>
         <v/>
       </c>
-      <c r="U15" s="55">
+      <c r="U15" s="173">
         <f>I15*$Q$3</f>
         <v/>
       </c>
-      <c r="V15" s="55">
+      <c r="V15" s="173">
         <f>J15*$Q$3</f>
         <v/>
       </c>
-      <c r="W15" s="55">
+      <c r="W15" s="173">
         <f>K15*$Q$3</f>
         <v/>
       </c>
-      <c r="X15" s="55">
+      <c r="X15" s="173">
         <f>L15*$Q$3</f>
         <v/>
       </c>
@@ -2296,48 +2671,48 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="40">
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="174" t="inlineStr">
         <is>
           <t>Artemisia</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="53" t="n"/>
-      <c r="H16" s="53" t="n"/>
-      <c r="I16" s="53" t="n"/>
-      <c r="J16" s="53" t="n"/>
-      <c r="K16" s="53" t="n"/>
-      <c r="L16" s="53" t="n"/>
-      <c r="M16" s="53" t="n"/>
-      <c r="P16" s="59" t="inlineStr">
+      <c r="E16" s="169" t="n"/>
+      <c r="F16" s="169" t="n"/>
+      <c r="G16" s="171" t="n"/>
+      <c r="H16" s="171" t="n"/>
+      <c r="I16" s="171" t="n"/>
+      <c r="J16" s="171" t="n"/>
+      <c r="K16" s="171" t="n"/>
+      <c r="L16" s="171" t="n"/>
+      <c r="M16" s="171" t="n"/>
+      <c r="P16" s="166" t="inlineStr">
         <is>
           <t>Artemisia</t>
         </is>
       </c>
-      <c r="Q16" s="46" t="n"/>
-      <c r="R16" s="47" t="n"/>
-      <c r="S16" s="55">
+      <c r="Q16" s="169" t="n"/>
+      <c r="R16" s="169" t="n"/>
+      <c r="S16" s="173">
         <f>G16*$Q$3</f>
         <v/>
       </c>
-      <c r="T16" s="55">
+      <c r="T16" s="173">
         <f>H16*$Q$3</f>
         <v/>
       </c>
-      <c r="U16" s="55">
+      <c r="U16" s="173">
         <f>I16*$Q$3</f>
         <v/>
       </c>
-      <c r="V16" s="55">
+      <c r="V16" s="173">
         <f>J16*$Q$3</f>
         <v/>
       </c>
-      <c r="W16" s="55">
+      <c r="W16" s="173">
         <f>K16*$Q$3</f>
         <v/>
       </c>
-      <c r="X16" s="55">
+      <c r="X16" s="173">
         <f>L16*$Q$3</f>
         <v/>
       </c>
@@ -2351,48 +2726,48 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="40">
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="175" t="inlineStr">
         <is>
           <t>CORYLACEAE (somma c+o)</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="47" t="n"/>
-      <c r="G17" s="61" t="n"/>
-      <c r="H17" s="61" t="n"/>
-      <c r="I17" s="61" t="n"/>
-      <c r="J17" s="61" t="n"/>
-      <c r="K17" s="61" t="n"/>
-      <c r="L17" s="61" t="n"/>
-      <c r="M17" s="61" t="n"/>
-      <c r="P17" s="62" t="inlineStr">
+      <c r="E17" s="169" t="n"/>
+      <c r="F17" s="169" t="n"/>
+      <c r="G17" s="176" t="n"/>
+      <c r="H17" s="176" t="n"/>
+      <c r="I17" s="176" t="n"/>
+      <c r="J17" s="176" t="n"/>
+      <c r="K17" s="176" t="n"/>
+      <c r="L17" s="176" t="n"/>
+      <c r="M17" s="176" t="n"/>
+      <c r="P17" s="177" t="inlineStr">
         <is>
           <t>CORYLACEAE (somma c+o)</t>
         </is>
       </c>
-      <c r="Q17" s="46" t="n"/>
-      <c r="R17" s="47" t="n"/>
-      <c r="S17" s="63">
+      <c r="Q17" s="169" t="n"/>
+      <c r="R17" s="169" t="n"/>
+      <c r="S17" s="178">
         <f>G17*$Q$3</f>
         <v/>
       </c>
-      <c r="T17" s="63">
+      <c r="T17" s="178">
         <f>H17*$Q$3</f>
         <v/>
       </c>
-      <c r="U17" s="63">
+      <c r="U17" s="178">
         <f>I17*$Q$3</f>
         <v/>
       </c>
-      <c r="V17" s="63">
+      <c r="V17" s="178">
         <f>J17*$Q$3</f>
         <v/>
       </c>
-      <c r="W17" s="63">
+      <c r="W17" s="178">
         <f>K17*$Q$3</f>
         <v/>
       </c>
-      <c r="X17" s="63">
+      <c r="X17" s="178">
         <f>L17*$Q$3</f>
         <v/>
       </c>
@@ -2406,48 +2781,48 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="40">
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="175" t="inlineStr">
         <is>
           <t>Carpinus/Ostrya</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
-      <c r="G18" s="61" t="n"/>
-      <c r="H18" s="61" t="n"/>
-      <c r="I18" s="61" t="n"/>
-      <c r="J18" s="61" t="n"/>
-      <c r="K18" s="61" t="n"/>
-      <c r="L18" s="61" t="n"/>
-      <c r="M18" s="61" t="n"/>
-      <c r="P18" s="62" t="inlineStr">
+      <c r="E18" s="169" t="n"/>
+      <c r="F18" s="169" t="n"/>
+      <c r="G18" s="176" t="n"/>
+      <c r="H18" s="176" t="n"/>
+      <c r="I18" s="176" t="n"/>
+      <c r="J18" s="176" t="n"/>
+      <c r="K18" s="176" t="n"/>
+      <c r="L18" s="176" t="n"/>
+      <c r="M18" s="176" t="n"/>
+      <c r="P18" s="177" t="inlineStr">
         <is>
           <t>Carpinus/Ostrya</t>
         </is>
       </c>
-      <c r="Q18" s="46" t="n"/>
-      <c r="R18" s="47" t="n"/>
-      <c r="S18" s="63">
+      <c r="Q18" s="169" t="n"/>
+      <c r="R18" s="169" t="n"/>
+      <c r="S18" s="178">
         <f>G18*$Q$3</f>
         <v/>
       </c>
-      <c r="T18" s="63">
+      <c r="T18" s="178">
         <f>H18*$Q$3</f>
         <v/>
       </c>
-      <c r="U18" s="63">
+      <c r="U18" s="178">
         <f>I18*$Q$3</f>
         <v/>
       </c>
-      <c r="V18" s="63">
+      <c r="V18" s="178">
         <f>J18*$Q$3</f>
         <v/>
       </c>
-      <c r="W18" s="63">
+      <c r="W18" s="178">
         <f>K18*$Q$3</f>
         <v/>
       </c>
-      <c r="X18" s="63">
+      <c r="X18" s="178">
         <f>L18*$Q$3</f>
         <v/>
       </c>
@@ -2461,48 +2836,48 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="40">
-      <c r="D19" s="66" t="inlineStr">
+      <c r="D19" s="179" t="inlineStr">
         <is>
           <t>Carpinus</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="47" t="n"/>
-      <c r="G19" s="61" t="n"/>
-      <c r="H19" s="61" t="n"/>
-      <c r="I19" s="61" t="n"/>
-      <c r="J19" s="61" t="n"/>
-      <c r="K19" s="61" t="n"/>
-      <c r="L19" s="61" t="n"/>
-      <c r="M19" s="61" t="n"/>
-      <c r="P19" s="67" t="inlineStr">
+      <c r="E19" s="169" t="n"/>
+      <c r="F19" s="169" t="n"/>
+      <c r="G19" s="176" t="n"/>
+      <c r="H19" s="176" t="n"/>
+      <c r="I19" s="176" t="n"/>
+      <c r="J19" s="176" t="n"/>
+      <c r="K19" s="176" t="n"/>
+      <c r="L19" s="176" t="n"/>
+      <c r="M19" s="176" t="n"/>
+      <c r="P19" s="180" t="inlineStr">
         <is>
           <t>Carpinus</t>
         </is>
       </c>
-      <c r="Q19" s="46" t="n"/>
-      <c r="R19" s="47" t="n"/>
-      <c r="S19" s="63">
+      <c r="Q19" s="169" t="n"/>
+      <c r="R19" s="169" t="n"/>
+      <c r="S19" s="178">
         <f>G19*$Q$3</f>
         <v/>
       </c>
-      <c r="T19" s="63">
+      <c r="T19" s="178">
         <f>H19*$Q$3</f>
         <v/>
       </c>
-      <c r="U19" s="63">
+      <c r="U19" s="178">
         <f>I19*$Q$3</f>
         <v/>
       </c>
-      <c r="V19" s="63">
+      <c r="V19" s="178">
         <f>J19*$Q$3</f>
         <v/>
       </c>
-      <c r="W19" s="63">
+      <c r="W19" s="178">
         <f>K19*$Q$3</f>
         <v/>
       </c>
-      <c r="X19" s="63">
+      <c r="X19" s="178">
         <f>L19*$Q$3</f>
         <v/>
       </c>
@@ -2516,48 +2891,48 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="40">
-      <c r="D20" s="66" t="inlineStr">
+      <c r="D20" s="179" t="inlineStr">
         <is>
           <t>Ostrya carpinifolia</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="61" t="n"/>
-      <c r="H20" s="61" t="n"/>
-      <c r="I20" s="61" t="n"/>
-      <c r="J20" s="61" t="n"/>
-      <c r="K20" s="61" t="n"/>
-      <c r="L20" s="61" t="n"/>
-      <c r="M20" s="61" t="n"/>
-      <c r="P20" s="67" t="inlineStr">
+      <c r="E20" s="169" t="n"/>
+      <c r="F20" s="169" t="n"/>
+      <c r="G20" s="176" t="n"/>
+      <c r="H20" s="176" t="n"/>
+      <c r="I20" s="176" t="n"/>
+      <c r="J20" s="176" t="n"/>
+      <c r="K20" s="176" t="n"/>
+      <c r="L20" s="176" t="n"/>
+      <c r="M20" s="176" t="n"/>
+      <c r="P20" s="180" t="inlineStr">
         <is>
           <t>Ostrya carpinifolia</t>
         </is>
       </c>
-      <c r="Q20" s="46" t="n"/>
-      <c r="R20" s="47" t="n"/>
-      <c r="S20" s="63">
+      <c r="Q20" s="169" t="n"/>
+      <c r="R20" s="169" t="n"/>
+      <c r="S20" s="178">
         <f>G20*$Q$3</f>
         <v/>
       </c>
-      <c r="T20" s="63">
+      <c r="T20" s="178">
         <f>H20*$Q$3</f>
         <v/>
       </c>
-      <c r="U20" s="63">
+      <c r="U20" s="178">
         <f>I20*$Q$3</f>
         <v/>
       </c>
-      <c r="V20" s="63">
+      <c r="V20" s="178">
         <f>J20*$Q$3</f>
         <v/>
       </c>
-      <c r="W20" s="63">
+      <c r="W20" s="178">
         <f>K20*$Q$3</f>
         <v/>
       </c>
-      <c r="X20" s="63">
+      <c r="X20" s="178">
         <f>L20*$Q$3</f>
         <v/>
       </c>
@@ -2571,48 +2946,48 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="40">
-      <c r="D21" s="58" t="inlineStr">
+      <c r="D21" s="174" t="inlineStr">
         <is>
           <t>Corylus avellana</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="47" t="n"/>
-      <c r="G21" s="53" t="n"/>
-      <c r="H21" s="53" t="n"/>
-      <c r="I21" s="53" t="n"/>
-      <c r="J21" s="53" t="n"/>
-      <c r="K21" s="53" t="n"/>
-      <c r="L21" s="53" t="n"/>
-      <c r="M21" s="53" t="n"/>
-      <c r="P21" s="59" t="inlineStr">
+      <c r="E21" s="169" t="n"/>
+      <c r="F21" s="169" t="n"/>
+      <c r="G21" s="171" t="n"/>
+      <c r="H21" s="171" t="n"/>
+      <c r="I21" s="171" t="n"/>
+      <c r="J21" s="171" t="n"/>
+      <c r="K21" s="171" t="n"/>
+      <c r="L21" s="171" t="n"/>
+      <c r="M21" s="171" t="n"/>
+      <c r="P21" s="166" t="inlineStr">
         <is>
           <t>Corylus avellana</t>
         </is>
       </c>
-      <c r="Q21" s="46" t="n"/>
-      <c r="R21" s="47" t="n"/>
-      <c r="S21" s="55">
+      <c r="Q21" s="169" t="n"/>
+      <c r="R21" s="169" t="n"/>
+      <c r="S21" s="173">
         <f>G21*$Q$3</f>
         <v/>
       </c>
-      <c r="T21" s="55">
+      <c r="T21" s="173">
         <f>H21*$Q$3</f>
         <v/>
       </c>
-      <c r="U21" s="55">
+      <c r="U21" s="173">
         <f>I21*$Q$3</f>
         <v/>
       </c>
-      <c r="V21" s="55">
+      <c r="V21" s="173">
         <f>J21*$Q$3</f>
         <v/>
       </c>
-      <c r="W21" s="55">
+      <c r="W21" s="173">
         <f>K21*$Q$3</f>
         <v/>
       </c>
-      <c r="X21" s="55">
+      <c r="X21" s="173">
         <f>L21*$Q$3</f>
         <v/>
       </c>
@@ -2626,48 +3001,48 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="40">
-      <c r="D22" s="60" t="inlineStr">
+      <c r="D22" s="175" t="inlineStr">
         <is>
           <t>CUP-TAXACEAE</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="61" t="n"/>
-      <c r="I22" s="61" t="n"/>
-      <c r="J22" s="61" t="n"/>
-      <c r="K22" s="61" t="n"/>
-      <c r="L22" s="61" t="n"/>
-      <c r="M22" s="61" t="n"/>
-      <c r="P22" s="62" t="inlineStr">
+      <c r="E22" s="169" t="n"/>
+      <c r="F22" s="169" t="n"/>
+      <c r="G22" s="176" t="n"/>
+      <c r="H22" s="176" t="n"/>
+      <c r="I22" s="176" t="n"/>
+      <c r="J22" s="176" t="n"/>
+      <c r="K22" s="176" t="n"/>
+      <c r="L22" s="176" t="n"/>
+      <c r="M22" s="176" t="n"/>
+      <c r="P22" s="177" t="inlineStr">
         <is>
           <t>CUP-TAXACEAE</t>
         </is>
       </c>
-      <c r="Q22" s="46" t="n"/>
-      <c r="R22" s="47" t="n"/>
-      <c r="S22" s="63">
+      <c r="Q22" s="169" t="n"/>
+      <c r="R22" s="169" t="n"/>
+      <c r="S22" s="178">
         <f>G22*$Q$3</f>
         <v/>
       </c>
-      <c r="T22" s="63">
+      <c r="T22" s="178">
         <f>H22*$Q$3</f>
         <v/>
       </c>
-      <c r="U22" s="63">
+      <c r="U22" s="178">
         <f>I22*$Q$3</f>
         <v/>
       </c>
-      <c r="V22" s="63">
+      <c r="V22" s="178">
         <f>J22*$Q$3</f>
         <v/>
       </c>
-      <c r="W22" s="63">
+      <c r="W22" s="178">
         <f>K22*$Q$3</f>
         <v/>
       </c>
-      <c r="X22" s="63">
+      <c r="X22" s="178">
         <f>L22*$Q$3</f>
         <v/>
       </c>
@@ -2681,48 +3056,48 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="40">
-      <c r="D23" s="66" t="inlineStr">
+      <c r="D23" s="179" t="inlineStr">
         <is>
           <t>ERICACEAE</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="61" t="n"/>
-      <c r="H23" s="61" t="n"/>
-      <c r="I23" s="61" t="n"/>
-      <c r="J23" s="61" t="n"/>
-      <c r="K23" s="61" t="n"/>
-      <c r="L23" s="61" t="n"/>
-      <c r="M23" s="61" t="n"/>
-      <c r="P23" s="67" t="inlineStr">
+      <c r="E23" s="169" t="n"/>
+      <c r="F23" s="169" t="n"/>
+      <c r="G23" s="176" t="n"/>
+      <c r="H23" s="176" t="n"/>
+      <c r="I23" s="176" t="n"/>
+      <c r="J23" s="176" t="n"/>
+      <c r="K23" s="176" t="n"/>
+      <c r="L23" s="176" t="n"/>
+      <c r="M23" s="176" t="n"/>
+      <c r="P23" s="180" t="inlineStr">
         <is>
           <t>ERICACEAE</t>
         </is>
       </c>
-      <c r="Q23" s="46" t="n"/>
-      <c r="R23" s="47" t="n"/>
-      <c r="S23" s="63">
+      <c r="Q23" s="169" t="n"/>
+      <c r="R23" s="169" t="n"/>
+      <c r="S23" s="178">
         <f>G23*$Q$3</f>
         <v/>
       </c>
-      <c r="T23" s="63">
+      <c r="T23" s="178">
         <f>H23*$Q$3</f>
         <v/>
       </c>
-      <c r="U23" s="63">
+      <c r="U23" s="178">
         <f>I23*$Q$3</f>
         <v/>
       </c>
-      <c r="V23" s="63">
+      <c r="V23" s="178">
         <f>J23*$Q$3</f>
         <v/>
       </c>
-      <c r="W23" s="63">
+      <c r="W23" s="178">
         <f>K23*$Q$3</f>
         <v/>
       </c>
-      <c r="X23" s="63">
+      <c r="X23" s="178">
         <f>L23*$Q$3</f>
         <v/>
       </c>
@@ -2736,48 +3111,48 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="40">
-      <c r="D24" s="66" t="inlineStr">
+      <c r="D24" s="179" t="inlineStr">
         <is>
           <t>EUPHORBIACEAE</t>
         </is>
       </c>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="47" t="n"/>
-      <c r="G24" s="61" t="n"/>
-      <c r="H24" s="61" t="n"/>
-      <c r="I24" s="61" t="n"/>
-      <c r="J24" s="61" t="n"/>
-      <c r="K24" s="61" t="n"/>
-      <c r="L24" s="61" t="n"/>
-      <c r="M24" s="61" t="n"/>
-      <c r="P24" s="67" t="inlineStr">
+      <c r="E24" s="169" t="n"/>
+      <c r="F24" s="169" t="n"/>
+      <c r="G24" s="176" t="n"/>
+      <c r="H24" s="176" t="n"/>
+      <c r="I24" s="176" t="n"/>
+      <c r="J24" s="176" t="n"/>
+      <c r="K24" s="176" t="n"/>
+      <c r="L24" s="176" t="n"/>
+      <c r="M24" s="176" t="n"/>
+      <c r="P24" s="180" t="inlineStr">
         <is>
           <t>EUPHORBIACEAE</t>
         </is>
       </c>
-      <c r="Q24" s="46" t="n"/>
-      <c r="R24" s="47" t="n"/>
-      <c r="S24" s="63">
+      <c r="Q24" s="169" t="n"/>
+      <c r="R24" s="169" t="n"/>
+      <c r="S24" s="178">
         <f>G24*$Q$3</f>
         <v/>
       </c>
-      <c r="T24" s="63">
+      <c r="T24" s="178">
         <f>H24*$Q$3</f>
         <v/>
       </c>
-      <c r="U24" s="63">
+      <c r="U24" s="178">
         <f>I24*$Q$3</f>
         <v/>
       </c>
-      <c r="V24" s="63">
+      <c r="V24" s="178">
         <f>J24*$Q$3</f>
         <v/>
       </c>
-      <c r="W24" s="63">
+      <c r="W24" s="178">
         <f>K24*$Q$3</f>
         <v/>
       </c>
-      <c r="X24" s="63">
+      <c r="X24" s="178">
         <f>L24*$Q$3</f>
         <v/>
       </c>
@@ -2791,48 +3166,48 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="40">
-      <c r="D25" s="58" t="inlineStr">
+      <c r="D25" s="174" t="inlineStr">
         <is>
           <t>FAGACEAE</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="47" t="n"/>
-      <c r="G25" s="53" t="n"/>
-      <c r="H25" s="53" t="n"/>
-      <c r="I25" s="53" t="n"/>
-      <c r="J25" s="53" t="n"/>
-      <c r="K25" s="53" t="n"/>
-      <c r="L25" s="53" t="n"/>
-      <c r="M25" s="53" t="n"/>
-      <c r="P25" s="59" t="inlineStr">
+      <c r="E25" s="169" t="n"/>
+      <c r="F25" s="169" t="n"/>
+      <c r="G25" s="171" t="n"/>
+      <c r="H25" s="171" t="n"/>
+      <c r="I25" s="171" t="n"/>
+      <c r="J25" s="171" t="n"/>
+      <c r="K25" s="171" t="n"/>
+      <c r="L25" s="171" t="n"/>
+      <c r="M25" s="171" t="n"/>
+      <c r="P25" s="166" t="inlineStr">
         <is>
           <t>FAGACEAE</t>
         </is>
       </c>
-      <c r="Q25" s="46" t="n"/>
-      <c r="R25" s="47" t="n"/>
-      <c r="S25" s="55">
+      <c r="Q25" s="169" t="n"/>
+      <c r="R25" s="169" t="n"/>
+      <c r="S25" s="173">
         <f>G25*$Q$3</f>
         <v/>
       </c>
-      <c r="T25" s="55">
+      <c r="T25" s="173">
         <f>H25*$Q$3</f>
         <v/>
       </c>
-      <c r="U25" s="55">
+      <c r="U25" s="173">
         <f>I25*$Q$3</f>
         <v/>
       </c>
-      <c r="V25" s="55">
+      <c r="V25" s="173">
         <f>J25*$Q$3</f>
         <v/>
       </c>
-      <c r="W25" s="55">
+      <c r="W25" s="173">
         <f>K25*$Q$3</f>
         <v/>
       </c>
-      <c r="X25" s="55">
+      <c r="X25" s="173">
         <f>L25*$Q$3</f>
         <v/>
       </c>
@@ -2846,48 +3221,48 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="40">
-      <c r="D26" s="58" t="inlineStr">
+      <c r="D26" s="174" t="inlineStr">
         <is>
           <t>Castanea sativa</t>
         </is>
       </c>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="47" t="n"/>
-      <c r="G26" s="53" t="n"/>
-      <c r="H26" s="53" t="n"/>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="53" t="n"/>
-      <c r="K26" s="53" t="n"/>
-      <c r="L26" s="53" t="n"/>
-      <c r="M26" s="53" t="n"/>
-      <c r="P26" s="59" t="inlineStr">
+      <c r="E26" s="169" t="n"/>
+      <c r="F26" s="169" t="n"/>
+      <c r="G26" s="171" t="n"/>
+      <c r="H26" s="171" t="n"/>
+      <c r="I26" s="171" t="n"/>
+      <c r="J26" s="171" t="n"/>
+      <c r="K26" s="171" t="n"/>
+      <c r="L26" s="171" t="n"/>
+      <c r="M26" s="171" t="n"/>
+      <c r="P26" s="166" t="inlineStr">
         <is>
           <t>Castanea sativa</t>
         </is>
       </c>
-      <c r="Q26" s="46" t="n"/>
-      <c r="R26" s="47" t="n"/>
-      <c r="S26" s="55">
+      <c r="Q26" s="169" t="n"/>
+      <c r="R26" s="169" t="n"/>
+      <c r="S26" s="173">
         <f>G26*$Q$3</f>
         <v/>
       </c>
-      <c r="T26" s="55">
+      <c r="T26" s="173">
         <f>H26*$Q$3</f>
         <v/>
       </c>
-      <c r="U26" s="55">
+      <c r="U26" s="173">
         <f>I26*$Q$3</f>
         <v/>
       </c>
-      <c r="V26" s="55">
+      <c r="V26" s="173">
         <f>J26*$Q$3</f>
         <v/>
       </c>
-      <c r="W26" s="55">
+      <c r="W26" s="173">
         <f>K26*$Q$3</f>
         <v/>
       </c>
-      <c r="X26" s="55">
+      <c r="X26" s="173">
         <f>L26*$Q$3</f>
         <v/>
       </c>
@@ -2901,48 +3276,48 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="40">
-      <c r="D27" s="60" t="inlineStr">
+      <c r="D27" s="175" t="inlineStr">
         <is>
           <t>Fagus sylvatica</t>
         </is>
       </c>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="47" t="n"/>
-      <c r="G27" s="61" t="n"/>
-      <c r="H27" s="61" t="n"/>
-      <c r="I27" s="61" t="n"/>
-      <c r="J27" s="61" t="n"/>
-      <c r="K27" s="61" t="n"/>
-      <c r="L27" s="61" t="n"/>
-      <c r="M27" s="61" t="n"/>
-      <c r="P27" s="62" t="inlineStr">
+      <c r="E27" s="169" t="n"/>
+      <c r="F27" s="169" t="n"/>
+      <c r="G27" s="176" t="n"/>
+      <c r="H27" s="176" t="n"/>
+      <c r="I27" s="176" t="n"/>
+      <c r="J27" s="176" t="n"/>
+      <c r="K27" s="176" t="n"/>
+      <c r="L27" s="176" t="n"/>
+      <c r="M27" s="176" t="n"/>
+      <c r="P27" s="177" t="inlineStr">
         <is>
           <t>Fagus sylvatica</t>
         </is>
       </c>
-      <c r="Q27" s="46" t="n"/>
-      <c r="R27" s="47" t="n"/>
-      <c r="S27" s="63">
+      <c r="Q27" s="169" t="n"/>
+      <c r="R27" s="169" t="n"/>
+      <c r="S27" s="178">
         <f>G27*$Q$3</f>
         <v/>
       </c>
-      <c r="T27" s="63">
+      <c r="T27" s="178">
         <f>H27*$Q$3</f>
         <v/>
       </c>
-      <c r="U27" s="63">
+      <c r="U27" s="178">
         <f>I27*$Q$3</f>
         <v/>
       </c>
-      <c r="V27" s="63">
+      <c r="V27" s="178">
         <f>J27*$Q$3</f>
         <v/>
       </c>
-      <c r="W27" s="63">
+      <c r="W27" s="178">
         <f>K27*$Q$3</f>
         <v/>
       </c>
-      <c r="X27" s="63">
+      <c r="X27" s="178">
         <f>L27*$Q$3</f>
         <v/>
       </c>
@@ -2956,48 +3331,48 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="40">
-      <c r="D28" s="60" t="inlineStr">
+      <c r="D28" s="175" t="inlineStr">
         <is>
           <t>Quercus</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="47" t="n"/>
-      <c r="G28" s="61" t="n"/>
-      <c r="H28" s="61" t="n"/>
-      <c r="I28" s="61" t="n"/>
-      <c r="J28" s="61" t="n"/>
-      <c r="K28" s="61" t="n"/>
-      <c r="L28" s="61" t="n"/>
-      <c r="M28" s="61" t="n"/>
-      <c r="P28" s="62" t="inlineStr">
+      <c r="E28" s="169" t="n"/>
+      <c r="F28" s="169" t="n"/>
+      <c r="G28" s="176" t="n"/>
+      <c r="H28" s="176" t="n"/>
+      <c r="I28" s="176" t="n"/>
+      <c r="J28" s="176" t="n"/>
+      <c r="K28" s="176" t="n"/>
+      <c r="L28" s="176" t="n"/>
+      <c r="M28" s="176" t="n"/>
+      <c r="P28" s="177" t="inlineStr">
         <is>
           <t>Quercus</t>
         </is>
       </c>
-      <c r="Q28" s="46" t="n"/>
-      <c r="R28" s="47" t="n"/>
-      <c r="S28" s="63">
+      <c r="Q28" s="169" t="n"/>
+      <c r="R28" s="169" t="n"/>
+      <c r="S28" s="178">
         <f>G28*$Q$3</f>
         <v/>
       </c>
-      <c r="T28" s="63">
+      <c r="T28" s="178">
         <f>H28*$Q$3</f>
         <v/>
       </c>
-      <c r="U28" s="63">
+      <c r="U28" s="178">
         <f>I28*$Q$3</f>
         <v/>
       </c>
-      <c r="V28" s="63">
+      <c r="V28" s="178">
         <f>J28*$Q$3</f>
         <v/>
       </c>
-      <c r="W28" s="63">
+      <c r="W28" s="178">
         <f>K28*$Q$3</f>
         <v/>
       </c>
-      <c r="X28" s="63">
+      <c r="X28" s="178">
         <f>L28*$Q$3</f>
         <v/>
       </c>
@@ -3011,48 +3386,48 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="40">
-      <c r="D29" s="60" t="inlineStr">
+      <c r="D29" s="175" t="inlineStr">
         <is>
           <t>GRAMINEAE</t>
         </is>
       </c>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="47" t="n"/>
-      <c r="G29" s="61" t="n"/>
-      <c r="H29" s="61" t="n"/>
-      <c r="I29" s="61" t="n"/>
-      <c r="J29" s="61" t="n"/>
-      <c r="K29" s="61" t="n"/>
-      <c r="L29" s="61" t="n"/>
-      <c r="M29" s="61" t="n"/>
-      <c r="P29" s="62" t="inlineStr">
+      <c r="E29" s="169" t="n"/>
+      <c r="F29" s="169" t="n"/>
+      <c r="G29" s="176" t="n"/>
+      <c r="H29" s="176" t="n"/>
+      <c r="I29" s="176" t="n"/>
+      <c r="J29" s="176" t="n"/>
+      <c r="K29" s="176" t="n"/>
+      <c r="L29" s="176" t="n"/>
+      <c r="M29" s="176" t="n"/>
+      <c r="P29" s="177" t="inlineStr">
         <is>
           <t>GRAMINEAE</t>
         </is>
       </c>
-      <c r="Q29" s="46" t="n"/>
-      <c r="R29" s="47" t="n"/>
-      <c r="S29" s="63">
+      <c r="Q29" s="169" t="n"/>
+      <c r="R29" s="169" t="n"/>
+      <c r="S29" s="178">
         <f>G29*$Q$3</f>
         <v/>
       </c>
-      <c r="T29" s="63">
+      <c r="T29" s="178">
         <f>H29*$Q$3</f>
         <v/>
       </c>
-      <c r="U29" s="63">
+      <c r="U29" s="178">
         <f>I29*$Q$3</f>
         <v/>
       </c>
-      <c r="V29" s="63">
+      <c r="V29" s="178">
         <f>J29*$Q$3</f>
         <v/>
       </c>
-      <c r="W29" s="63">
+      <c r="W29" s="178">
         <f>K29*$Q$3</f>
         <v/>
       </c>
-      <c r="X29" s="63">
+      <c r="X29" s="178">
         <f>L29*$Q$3</f>
         <v/>
       </c>
@@ -3066,48 +3441,48 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="40">
-      <c r="D30" s="51" t="inlineStr">
+      <c r="D30" s="168" t="inlineStr">
         <is>
           <t>HIPPOCASTANACEAE</t>
         </is>
       </c>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="47" t="n"/>
-      <c r="G30" s="53" t="n"/>
-      <c r="H30" s="53" t="n"/>
-      <c r="I30" s="53" t="n"/>
-      <c r="J30" s="53" t="n"/>
-      <c r="K30" s="53" t="n"/>
-      <c r="L30" s="53" t="n"/>
-      <c r="M30" s="53" t="n"/>
-      <c r="P30" s="54" t="inlineStr">
+      <c r="E30" s="169" t="n"/>
+      <c r="F30" s="169" t="n"/>
+      <c r="G30" s="171" t="n"/>
+      <c r="H30" s="171" t="n"/>
+      <c r="I30" s="171" t="n"/>
+      <c r="J30" s="171" t="n"/>
+      <c r="K30" s="171" t="n"/>
+      <c r="L30" s="171" t="n"/>
+      <c r="M30" s="171" t="n"/>
+      <c r="P30" s="172" t="inlineStr">
         <is>
           <t>HIPPOCASTANACEAE</t>
         </is>
       </c>
-      <c r="Q30" s="46" t="n"/>
-      <c r="R30" s="47" t="n"/>
-      <c r="S30" s="55">
+      <c r="Q30" s="169" t="n"/>
+      <c r="R30" s="169" t="n"/>
+      <c r="S30" s="173">
         <f>G30*$Q$3</f>
         <v/>
       </c>
-      <c r="T30" s="55">
+      <c r="T30" s="173">
         <f>H30*$Q$3</f>
         <v/>
       </c>
-      <c r="U30" s="55">
+      <c r="U30" s="173">
         <f>I30*$Q$3</f>
         <v/>
       </c>
-      <c r="V30" s="55">
+      <c r="V30" s="173">
         <f>J30*$Q$3</f>
         <v/>
       </c>
-      <c r="W30" s="55">
+      <c r="W30" s="173">
         <f>K30*$Q$3</f>
         <v/>
       </c>
-      <c r="X30" s="55">
+      <c r="X30" s="173">
         <f>L30*$Q$3</f>
         <v/>
       </c>
@@ -3121,48 +3496,48 @@
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="40">
-      <c r="D31" s="51" t="inlineStr">
+      <c r="D31" s="168" t="inlineStr">
         <is>
           <t>JUGLANDACEAE</t>
         </is>
       </c>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="47" t="n"/>
-      <c r="G31" s="53" t="n"/>
-      <c r="H31" s="53" t="n"/>
-      <c r="I31" s="53" t="n"/>
-      <c r="J31" s="53" t="n"/>
-      <c r="K31" s="53" t="n"/>
-      <c r="L31" s="53" t="n"/>
-      <c r="M31" s="53" t="n"/>
-      <c r="P31" s="54" t="inlineStr">
+      <c r="E31" s="169" t="n"/>
+      <c r="F31" s="169" t="n"/>
+      <c r="G31" s="171" t="n"/>
+      <c r="H31" s="171" t="n"/>
+      <c r="I31" s="171" t="n"/>
+      <c r="J31" s="171" t="n"/>
+      <c r="K31" s="171" t="n"/>
+      <c r="L31" s="171" t="n"/>
+      <c r="M31" s="171" t="n"/>
+      <c r="P31" s="172" t="inlineStr">
         <is>
           <t>JUGLANDACEAE</t>
         </is>
       </c>
-      <c r="Q31" s="46" t="n"/>
-      <c r="R31" s="47" t="n"/>
-      <c r="S31" s="55">
+      <c r="Q31" s="169" t="n"/>
+      <c r="R31" s="169" t="n"/>
+      <c r="S31" s="173">
         <f>G31*$Q$3</f>
         <v/>
       </c>
-      <c r="T31" s="55">
+      <c r="T31" s="173">
         <f>H31*$Q$3</f>
         <v/>
       </c>
-      <c r="U31" s="55">
+      <c r="U31" s="173">
         <f>I31*$Q$3</f>
         <v/>
       </c>
-      <c r="V31" s="55">
+      <c r="V31" s="173">
         <f>J31*$Q$3</f>
         <v/>
       </c>
-      <c r="W31" s="55">
+      <c r="W31" s="173">
         <f>K31*$Q$3</f>
         <v/>
       </c>
-      <c r="X31" s="55">
+      <c r="X31" s="173">
         <f>L31*$Q$3</f>
         <v/>
       </c>
@@ -3176,48 +3551,48 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="40">
-      <c r="D32" s="51" t="inlineStr">
+      <c r="D32" s="168" t="inlineStr">
         <is>
           <t>LAURACEAE</t>
         </is>
       </c>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="47" t="n"/>
-      <c r="G32" s="53" t="n"/>
-      <c r="H32" s="53" t="n"/>
-      <c r="I32" s="53" t="n"/>
-      <c r="J32" s="53" t="n"/>
-      <c r="K32" s="53" t="n"/>
-      <c r="L32" s="53" t="n"/>
-      <c r="M32" s="53" t="n"/>
-      <c r="P32" s="54" t="inlineStr">
+      <c r="E32" s="169" t="n"/>
+      <c r="F32" s="169" t="n"/>
+      <c r="G32" s="171" t="n"/>
+      <c r="H32" s="171" t="n"/>
+      <c r="I32" s="171" t="n"/>
+      <c r="J32" s="171" t="n"/>
+      <c r="K32" s="171" t="n"/>
+      <c r="L32" s="171" t="n"/>
+      <c r="M32" s="171" t="n"/>
+      <c r="P32" s="172" t="inlineStr">
         <is>
           <t>LAURACEAE</t>
         </is>
       </c>
-      <c r="Q32" s="46" t="n"/>
-      <c r="R32" s="47" t="n"/>
-      <c r="S32" s="55">
+      <c r="Q32" s="169" t="n"/>
+      <c r="R32" s="169" t="n"/>
+      <c r="S32" s="173">
         <f>G32*$Q$3</f>
         <v/>
       </c>
-      <c r="T32" s="55">
+      <c r="T32" s="173">
         <f>H32*$Q$3</f>
         <v/>
       </c>
-      <c r="U32" s="55">
+      <c r="U32" s="173">
         <f>I32*$Q$3</f>
         <v/>
       </c>
-      <c r="V32" s="55">
+      <c r="V32" s="173">
         <f>J32*$Q$3</f>
         <v/>
       </c>
-      <c r="W32" s="55">
+      <c r="W32" s="173">
         <f>K32*$Q$3</f>
         <v/>
       </c>
-      <c r="X32" s="55">
+      <c r="X32" s="173">
         <f>L32*$Q$3</f>
         <v/>
       </c>
@@ -3231,48 +3606,48 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="40">
-      <c r="D33" s="51" t="inlineStr">
+      <c r="D33" s="168" t="inlineStr">
         <is>
           <t>MIMOSACEAE</t>
         </is>
       </c>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="47" t="n"/>
-      <c r="G33" s="53" t="n"/>
-      <c r="H33" s="53" t="n"/>
-      <c r="I33" s="53" t="n"/>
-      <c r="J33" s="53" t="n"/>
-      <c r="K33" s="53" t="n"/>
-      <c r="L33" s="53" t="n"/>
-      <c r="M33" s="53" t="n"/>
-      <c r="P33" s="54" t="inlineStr">
+      <c r="E33" s="169" t="n"/>
+      <c r="F33" s="169" t="n"/>
+      <c r="G33" s="171" t="n"/>
+      <c r="H33" s="171" t="n"/>
+      <c r="I33" s="171" t="n"/>
+      <c r="J33" s="171" t="n"/>
+      <c r="K33" s="171" t="n"/>
+      <c r="L33" s="171" t="n"/>
+      <c r="M33" s="171" t="n"/>
+      <c r="P33" s="172" t="inlineStr">
         <is>
           <t>MIMOSACEAE</t>
         </is>
       </c>
-      <c r="Q33" s="46" t="n"/>
-      <c r="R33" s="47" t="n"/>
-      <c r="S33" s="55">
+      <c r="Q33" s="169" t="n"/>
+      <c r="R33" s="169" t="n"/>
+      <c r="S33" s="173">
         <f>G33*$Q$3</f>
         <v/>
       </c>
-      <c r="T33" s="55">
+      <c r="T33" s="173">
         <f>H33*$Q$3</f>
         <v/>
       </c>
-      <c r="U33" s="55">
+      <c r="U33" s="173">
         <f>I33*$Q$3</f>
         <v/>
       </c>
-      <c r="V33" s="55">
+      <c r="V33" s="173">
         <f>J33*$Q$3</f>
         <v/>
       </c>
-      <c r="W33" s="55">
+      <c r="W33" s="173">
         <f>K33*$Q$3</f>
         <v/>
       </c>
-      <c r="X33" s="55">
+      <c r="X33" s="173">
         <f>L33*$Q$3</f>
         <v/>
       </c>
@@ -3286,48 +3661,48 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="40">
-      <c r="D34" s="51" t="inlineStr">
+      <c r="D34" s="168" t="inlineStr">
         <is>
           <t>MORACEAE</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="47" t="n"/>
-      <c r="G34" s="53" t="n"/>
-      <c r="H34" s="53" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="53" t="n"/>
-      <c r="K34" s="53" t="n"/>
-      <c r="L34" s="53" t="n"/>
-      <c r="M34" s="53" t="n"/>
-      <c r="P34" s="54" t="inlineStr">
+      <c r="E34" s="169" t="n"/>
+      <c r="F34" s="169" t="n"/>
+      <c r="G34" s="171" t="n"/>
+      <c r="H34" s="171" t="n"/>
+      <c r="I34" s="171" t="n"/>
+      <c r="J34" s="171" t="n"/>
+      <c r="K34" s="171" t="n"/>
+      <c r="L34" s="171" t="n"/>
+      <c r="M34" s="171" t="n"/>
+      <c r="P34" s="172" t="inlineStr">
         <is>
           <t>MORACEAE</t>
         </is>
       </c>
-      <c r="Q34" s="46" t="n"/>
-      <c r="R34" s="47" t="n"/>
-      <c r="S34" s="55">
+      <c r="Q34" s="169" t="n"/>
+      <c r="R34" s="169" t="n"/>
+      <c r="S34" s="173">
         <f>G34*$Q$3</f>
         <v/>
       </c>
-      <c r="T34" s="55">
+      <c r="T34" s="173">
         <f>H34*$Q$3</f>
         <v/>
       </c>
-      <c r="U34" s="55">
+      <c r="U34" s="173">
         <f>I34*$Q$3</f>
         <v/>
       </c>
-      <c r="V34" s="55">
+      <c r="V34" s="173">
         <f>J34*$Q$3</f>
         <v/>
       </c>
-      <c r="W34" s="55">
+      <c r="W34" s="173">
         <f>K34*$Q$3</f>
         <v/>
       </c>
-      <c r="X34" s="55">
+      <c r="X34" s="173">
         <f>L34*$Q$3</f>
         <v/>
       </c>
@@ -3341,48 +3716,48 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="40">
-      <c r="D35" s="51" t="inlineStr">
+      <c r="D35" s="168" t="inlineStr">
         <is>
           <t>MYRTACEAE</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="47" t="n"/>
-      <c r="G35" s="53" t="n"/>
-      <c r="H35" s="53" t="n"/>
-      <c r="I35" s="53" t="n"/>
-      <c r="J35" s="53" t="n"/>
-      <c r="K35" s="53" t="n"/>
-      <c r="L35" s="53" t="n"/>
-      <c r="M35" s="53" t="n"/>
-      <c r="P35" s="54" t="inlineStr">
+      <c r="E35" s="169" t="n"/>
+      <c r="F35" s="169" t="n"/>
+      <c r="G35" s="171" t="n"/>
+      <c r="H35" s="171" t="n"/>
+      <c r="I35" s="171" t="n"/>
+      <c r="J35" s="171" t="n"/>
+      <c r="K35" s="171" t="n"/>
+      <c r="L35" s="171" t="n"/>
+      <c r="M35" s="171" t="n"/>
+      <c r="P35" s="172" t="inlineStr">
         <is>
           <t>MYRTACEAE</t>
         </is>
       </c>
-      <c r="Q35" s="46" t="n"/>
-      <c r="R35" s="47" t="n"/>
-      <c r="S35" s="55">
+      <c r="Q35" s="169" t="n"/>
+      <c r="R35" s="169" t="n"/>
+      <c r="S35" s="173">
         <f>G35*$Q$3</f>
         <v/>
       </c>
-      <c r="T35" s="55">
+      <c r="T35" s="173">
         <f>H35*$Q$3</f>
         <v/>
       </c>
-      <c r="U35" s="55">
+      <c r="U35" s="173">
         <f>I35*$Q$3</f>
         <v/>
       </c>
-      <c r="V35" s="55">
+      <c r="V35" s="173">
         <f>J35*$Q$3</f>
         <v/>
       </c>
-      <c r="W35" s="55">
+      <c r="W35" s="173">
         <f>K35*$Q$3</f>
         <v/>
       </c>
-      <c r="X35" s="55">
+      <c r="X35" s="173">
         <f>L35*$Q$3</f>
         <v/>
       </c>
@@ -3396,48 +3771,48 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="40">
-      <c r="D36" s="58" t="inlineStr">
+      <c r="D36" s="174" t="inlineStr">
         <is>
           <t>OLEACEAE</t>
         </is>
       </c>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="47" t="n"/>
-      <c r="G36" s="53" t="n"/>
-      <c r="H36" s="53" t="n"/>
-      <c r="I36" s="53" t="n"/>
-      <c r="J36" s="53" t="n"/>
-      <c r="K36" s="53" t="n"/>
-      <c r="L36" s="53" t="n"/>
-      <c r="M36" s="53" t="n"/>
-      <c r="P36" s="59" t="inlineStr">
+      <c r="E36" s="169" t="n"/>
+      <c r="F36" s="169" t="n"/>
+      <c r="G36" s="171" t="n"/>
+      <c r="H36" s="171" t="n"/>
+      <c r="I36" s="171" t="n"/>
+      <c r="J36" s="171" t="n"/>
+      <c r="K36" s="171" t="n"/>
+      <c r="L36" s="171" t="n"/>
+      <c r="M36" s="171" t="n"/>
+      <c r="P36" s="166" t="inlineStr">
         <is>
           <t>OLEACEAE</t>
         </is>
       </c>
-      <c r="Q36" s="46" t="n"/>
-      <c r="R36" s="47" t="n"/>
-      <c r="S36" s="55">
+      <c r="Q36" s="169" t="n"/>
+      <c r="R36" s="169" t="n"/>
+      <c r="S36" s="173">
         <f>G36*$Q$3</f>
         <v/>
       </c>
-      <c r="T36" s="55">
+      <c r="T36" s="173">
         <f>H36*$Q$3</f>
         <v/>
       </c>
-      <c r="U36" s="55">
+      <c r="U36" s="173">
         <f>I36*$Q$3</f>
         <v/>
       </c>
-      <c r="V36" s="55">
+      <c r="V36" s="173">
         <f>J36*$Q$3</f>
         <v/>
       </c>
-      <c r="W36" s="55">
+      <c r="W36" s="173">
         <f>K36*$Q$3</f>
         <v/>
       </c>
-      <c r="X36" s="55">
+      <c r="X36" s="173">
         <f>L36*$Q$3</f>
         <v/>
       </c>
@@ -3451,48 +3826,48 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="40">
-      <c r="D37" s="58" t="inlineStr">
+      <c r="D37" s="174" t="inlineStr">
         <is>
           <t>Altre oleaceae</t>
         </is>
       </c>
-      <c r="E37" s="46" t="n"/>
-      <c r="F37" s="47" t="n"/>
-      <c r="G37" s="53" t="n"/>
-      <c r="H37" s="53" t="n"/>
-      <c r="I37" s="53" t="n"/>
-      <c r="J37" s="53" t="n"/>
-      <c r="K37" s="53" t="n"/>
-      <c r="L37" s="53" t="n"/>
-      <c r="M37" s="53" t="n"/>
-      <c r="P37" s="59" t="inlineStr">
+      <c r="E37" s="169" t="n"/>
+      <c r="F37" s="169" t="n"/>
+      <c r="G37" s="171" t="n"/>
+      <c r="H37" s="171" t="n"/>
+      <c r="I37" s="171" t="n"/>
+      <c r="J37" s="171" t="n"/>
+      <c r="K37" s="171" t="n"/>
+      <c r="L37" s="171" t="n"/>
+      <c r="M37" s="171" t="n"/>
+      <c r="P37" s="166" t="inlineStr">
         <is>
           <t>Altre oleaceae</t>
         </is>
       </c>
-      <c r="Q37" s="46" t="n"/>
-      <c r="R37" s="47" t="n"/>
-      <c r="S37" s="55">
+      <c r="Q37" s="169" t="n"/>
+      <c r="R37" s="169" t="n"/>
+      <c r="S37" s="173">
         <f>G37*$Q$3</f>
         <v/>
       </c>
-      <c r="T37" s="55">
+      <c r="T37" s="173">
         <f>H37*$Q$3</f>
         <v/>
       </c>
-      <c r="U37" s="55">
+      <c r="U37" s="173">
         <f>I37*$Q$3</f>
         <v/>
       </c>
-      <c r="V37" s="55">
+      <c r="V37" s="173">
         <f>J37*$Q$3</f>
         <v/>
       </c>
-      <c r="W37" s="55">
+      <c r="W37" s="173">
         <f>K37*$Q$3</f>
         <v/>
       </c>
-      <c r="X37" s="55">
+      <c r="X37" s="173">
         <f>L37*$Q$3</f>
         <v/>
       </c>
@@ -3506,48 +3881,48 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="40">
-      <c r="D38" s="60" t="inlineStr">
+      <c r="D38" s="175" t="inlineStr">
         <is>
           <t>Fraxinus</t>
         </is>
       </c>
-      <c r="E38" s="46" t="n"/>
-      <c r="F38" s="47" t="n"/>
-      <c r="G38" s="61" t="n"/>
-      <c r="H38" s="61" t="n"/>
-      <c r="I38" s="61" t="n"/>
-      <c r="J38" s="61" t="n"/>
-      <c r="K38" s="61" t="n"/>
-      <c r="L38" s="61" t="n"/>
-      <c r="M38" s="61" t="n"/>
-      <c r="P38" s="62" t="inlineStr">
+      <c r="E38" s="169" t="n"/>
+      <c r="F38" s="169" t="n"/>
+      <c r="G38" s="176" t="n"/>
+      <c r="H38" s="176" t="n"/>
+      <c r="I38" s="176" t="n"/>
+      <c r="J38" s="176" t="n"/>
+      <c r="K38" s="176" t="n"/>
+      <c r="L38" s="176" t="n"/>
+      <c r="M38" s="176" t="n"/>
+      <c r="P38" s="177" t="inlineStr">
         <is>
           <t>Fraxinus</t>
         </is>
       </c>
-      <c r="Q38" s="46" t="n"/>
-      <c r="R38" s="47" t="n"/>
-      <c r="S38" s="63">
+      <c r="Q38" s="169" t="n"/>
+      <c r="R38" s="169" t="n"/>
+      <c r="S38" s="178">
         <f>G38*$Q$3</f>
         <v/>
       </c>
-      <c r="T38" s="63">
+      <c r="T38" s="178">
         <f>H38*$Q$3</f>
         <v/>
       </c>
-      <c r="U38" s="63">
+      <c r="U38" s="178">
         <f>I38*$Q$3</f>
         <v/>
       </c>
-      <c r="V38" s="63">
+      <c r="V38" s="178">
         <f>J38*$Q$3</f>
         <v/>
       </c>
-      <c r="W38" s="63">
+      <c r="W38" s="178">
         <f>K38*$Q$3</f>
         <v/>
       </c>
-      <c r="X38" s="63">
+      <c r="X38" s="178">
         <f>L38*$Q$3</f>
         <v/>
       </c>
@@ -3561,48 +3936,48 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="40">
-      <c r="D39" s="58" t="inlineStr">
+      <c r="D39" s="174" t="inlineStr">
         <is>
           <t>Ligustrum</t>
         </is>
       </c>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="47" t="n"/>
-      <c r="G39" s="53" t="n"/>
-      <c r="H39" s="53" t="n"/>
-      <c r="I39" s="53" t="n"/>
-      <c r="J39" s="53" t="n"/>
-      <c r="K39" s="53" t="n"/>
-      <c r="L39" s="53" t="n"/>
-      <c r="M39" s="53" t="n"/>
-      <c r="P39" s="59" t="inlineStr">
+      <c r="E39" s="169" t="n"/>
+      <c r="F39" s="169" t="n"/>
+      <c r="G39" s="171" t="n"/>
+      <c r="H39" s="171" t="n"/>
+      <c r="I39" s="171" t="n"/>
+      <c r="J39" s="171" t="n"/>
+      <c r="K39" s="171" t="n"/>
+      <c r="L39" s="171" t="n"/>
+      <c r="M39" s="171" t="n"/>
+      <c r="P39" s="166" t="inlineStr">
         <is>
           <t>Ligustrum</t>
         </is>
       </c>
-      <c r="Q39" s="46" t="n"/>
-      <c r="R39" s="47" t="n"/>
-      <c r="S39" s="55">
+      <c r="Q39" s="169" t="n"/>
+      <c r="R39" s="169" t="n"/>
+      <c r="S39" s="173">
         <f>G39*$Q$3</f>
         <v/>
       </c>
-      <c r="T39" s="55">
+      <c r="T39" s="173">
         <f>H39*$Q$3</f>
         <v/>
       </c>
-      <c r="U39" s="55">
+      <c r="U39" s="173">
         <f>I39*$Q$3</f>
         <v/>
       </c>
-      <c r="V39" s="55">
+      <c r="V39" s="173">
         <f>J39*$Q$3</f>
         <v/>
       </c>
-      <c r="W39" s="55">
+      <c r="W39" s="173">
         <f>K39*$Q$3</f>
         <v/>
       </c>
-      <c r="X39" s="55">
+      <c r="X39" s="173">
         <f>L39*$Q$3</f>
         <v/>
       </c>
@@ -3616,48 +3991,48 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="40">
-      <c r="D40" s="60" t="inlineStr">
+      <c r="D40" s="175" t="inlineStr">
         <is>
           <t>Olea</t>
         </is>
       </c>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="47" t="n"/>
-      <c r="G40" s="61" t="n"/>
-      <c r="H40" s="61" t="n"/>
-      <c r="I40" s="61" t="n"/>
-      <c r="J40" s="61" t="n"/>
-      <c r="K40" s="61" t="n"/>
-      <c r="L40" s="61" t="n"/>
-      <c r="M40" s="61" t="n"/>
-      <c r="P40" s="62" t="inlineStr">
+      <c r="E40" s="169" t="n"/>
+      <c r="F40" s="169" t="n"/>
+      <c r="G40" s="176" t="n"/>
+      <c r="H40" s="176" t="n"/>
+      <c r="I40" s="176" t="n"/>
+      <c r="J40" s="176" t="n"/>
+      <c r="K40" s="176" t="n"/>
+      <c r="L40" s="176" t="n"/>
+      <c r="M40" s="176" t="n"/>
+      <c r="P40" s="177" t="inlineStr">
         <is>
           <t>Olea</t>
         </is>
       </c>
-      <c r="Q40" s="46" t="n"/>
-      <c r="R40" s="47" t="n"/>
-      <c r="S40" s="63">
+      <c r="Q40" s="169" t="n"/>
+      <c r="R40" s="169" t="n"/>
+      <c r="S40" s="178">
         <f>G40*$Q$3</f>
         <v/>
       </c>
-      <c r="T40" s="63">
+      <c r="T40" s="178">
         <f>H40*$Q$3</f>
         <v/>
       </c>
-      <c r="U40" s="63">
+      <c r="U40" s="178">
         <f>I40*$Q$3</f>
         <v/>
       </c>
-      <c r="V40" s="63">
+      <c r="V40" s="178">
         <f>J40*$Q$3</f>
         <v/>
       </c>
-      <c r="W40" s="63">
+      <c r="W40" s="178">
         <f>K40*$Q$3</f>
         <v/>
       </c>
-      <c r="X40" s="63">
+      <c r="X40" s="178">
         <f>L40*$Q$3</f>
         <v/>
       </c>
@@ -3671,48 +4046,48 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="40">
-      <c r="D41" s="66" t="inlineStr">
+      <c r="D41" s="179" t="inlineStr">
         <is>
           <t>PINACEAE</t>
         </is>
       </c>
-      <c r="E41" s="46" t="n"/>
-      <c r="F41" s="47" t="n"/>
-      <c r="G41" s="61" t="n"/>
-      <c r="H41" s="61" t="n"/>
-      <c r="I41" s="61" t="n"/>
-      <c r="J41" s="61" t="n"/>
-      <c r="K41" s="61" t="n"/>
-      <c r="L41" s="61" t="n"/>
-      <c r="M41" s="61" t="n"/>
-      <c r="P41" s="67" t="inlineStr">
+      <c r="E41" s="169" t="n"/>
+      <c r="F41" s="169" t="n"/>
+      <c r="G41" s="176" t="n"/>
+      <c r="H41" s="176" t="n"/>
+      <c r="I41" s="176" t="n"/>
+      <c r="J41" s="176" t="n"/>
+      <c r="K41" s="176" t="n"/>
+      <c r="L41" s="176" t="n"/>
+      <c r="M41" s="176" t="n"/>
+      <c r="P41" s="180" t="inlineStr">
         <is>
           <t>PINACEAE</t>
         </is>
       </c>
-      <c r="Q41" s="46" t="n"/>
-      <c r="R41" s="47" t="n"/>
-      <c r="S41" s="63">
+      <c r="Q41" s="169" t="n"/>
+      <c r="R41" s="169" t="n"/>
+      <c r="S41" s="178">
         <f>G41*$Q$3</f>
         <v/>
       </c>
-      <c r="T41" s="63">
+      <c r="T41" s="178">
         <f>H41*$Q$3</f>
         <v/>
       </c>
-      <c r="U41" s="63">
+      <c r="U41" s="178">
         <f>I41*$Q$3</f>
         <v/>
       </c>
-      <c r="V41" s="63">
+      <c r="V41" s="178">
         <f>J41*$Q$3</f>
         <v/>
       </c>
-      <c r="W41" s="63">
+      <c r="W41" s="178">
         <f>K41*$Q$3</f>
         <v/>
       </c>
-      <c r="X41" s="63">
+      <c r="X41" s="178">
         <f>L41*$Q$3</f>
         <v/>
       </c>
@@ -3726,48 +4101,48 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="40">
-      <c r="D42" s="51" t="inlineStr">
+      <c r="D42" s="168" t="inlineStr">
         <is>
           <t>PLANTAGINACEAE</t>
         </is>
       </c>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="47" t="n"/>
-      <c r="G42" s="53" t="n"/>
-      <c r="H42" s="53" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="53" t="n"/>
-      <c r="K42" s="53" t="n"/>
-      <c r="L42" s="53" t="n"/>
-      <c r="M42" s="53" t="n"/>
-      <c r="P42" s="54" t="inlineStr">
+      <c r="E42" s="169" t="n"/>
+      <c r="F42" s="169" t="n"/>
+      <c r="G42" s="171" t="n"/>
+      <c r="H42" s="171" t="n"/>
+      <c r="I42" s="171" t="n"/>
+      <c r="J42" s="171" t="n"/>
+      <c r="K42" s="171" t="n"/>
+      <c r="L42" s="171" t="n"/>
+      <c r="M42" s="171" t="n"/>
+      <c r="P42" s="172" t="inlineStr">
         <is>
           <t>PLANTAGINACEAE</t>
         </is>
       </c>
-      <c r="Q42" s="46" t="n"/>
-      <c r="R42" s="47" t="n"/>
-      <c r="S42" s="55">
+      <c r="Q42" s="169" t="n"/>
+      <c r="R42" s="169" t="n"/>
+      <c r="S42" s="173">
         <f>G42*$Q$3</f>
         <v/>
       </c>
-      <c r="T42" s="55">
+      <c r="T42" s="173">
         <f>H42*$Q$3</f>
         <v/>
       </c>
-      <c r="U42" s="55">
+      <c r="U42" s="173">
         <f>I42*$Q$3</f>
         <v/>
       </c>
-      <c r="V42" s="55">
+      <c r="V42" s="173">
         <f>J42*$Q$3</f>
         <v/>
       </c>
-      <c r="W42" s="55">
+      <c r="W42" s="173">
         <f>K42*$Q$3</f>
         <v/>
       </c>
-      <c r="X42" s="55">
+      <c r="X42" s="173">
         <f>L42*$Q$3</f>
         <v/>
       </c>
@@ -3781,48 +4156,48 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="40">
-      <c r="D43" s="51" t="inlineStr">
+      <c r="D43" s="168" t="inlineStr">
         <is>
           <t>PLATANACEAE</t>
         </is>
       </c>
-      <c r="E43" s="46" t="n"/>
-      <c r="F43" s="47" t="n"/>
-      <c r="G43" s="53" t="n"/>
-      <c r="H43" s="53" t="n"/>
-      <c r="I43" s="53" t="n"/>
-      <c r="J43" s="53" t="n"/>
-      <c r="K43" s="53" t="n"/>
-      <c r="L43" s="53" t="n"/>
-      <c r="M43" s="53" t="n"/>
-      <c r="P43" s="54" t="inlineStr">
+      <c r="E43" s="169" t="n"/>
+      <c r="F43" s="169" t="n"/>
+      <c r="G43" s="171" t="n"/>
+      <c r="H43" s="171" t="n"/>
+      <c r="I43" s="171" t="n"/>
+      <c r="J43" s="171" t="n"/>
+      <c r="K43" s="171" t="n"/>
+      <c r="L43" s="171" t="n"/>
+      <c r="M43" s="171" t="n"/>
+      <c r="P43" s="172" t="inlineStr">
         <is>
           <t>PLATANACEAE</t>
         </is>
       </c>
-      <c r="Q43" s="46" t="n"/>
-      <c r="R43" s="47" t="n"/>
-      <c r="S43" s="55">
+      <c r="Q43" s="169" t="n"/>
+      <c r="R43" s="169" t="n"/>
+      <c r="S43" s="173">
         <f>G43*$Q$3</f>
         <v/>
       </c>
-      <c r="T43" s="55">
+      <c r="T43" s="173">
         <f>H43*$Q$3</f>
         <v/>
       </c>
-      <c r="U43" s="55">
+      <c r="U43" s="173">
         <f>I43*$Q$3</f>
         <v/>
       </c>
-      <c r="V43" s="55">
+      <c r="V43" s="173">
         <f>J43*$Q$3</f>
         <v/>
       </c>
-      <c r="W43" s="55">
+      <c r="W43" s="173">
         <f>K43*$Q$3</f>
         <v/>
       </c>
-      <c r="X43" s="55">
+      <c r="X43" s="173">
         <f>L43*$Q$3</f>
         <v/>
       </c>
@@ -3836,48 +4211,48 @@
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="40">
-      <c r="D44" s="58" t="inlineStr">
+      <c r="D44" s="174" t="inlineStr">
         <is>
           <t>POLLINI NON IDENTIFICATI</t>
         </is>
       </c>
-      <c r="E44" s="46" t="n"/>
-      <c r="F44" s="47" t="n"/>
-      <c r="G44" s="53" t="n"/>
-      <c r="H44" s="53" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="53" t="n"/>
-      <c r="K44" s="53" t="n"/>
-      <c r="L44" s="53" t="n"/>
-      <c r="M44" s="53" t="n"/>
-      <c r="P44" s="59" t="inlineStr">
+      <c r="E44" s="169" t="n"/>
+      <c r="F44" s="169" t="n"/>
+      <c r="G44" s="171" t="n"/>
+      <c r="H44" s="171" t="n"/>
+      <c r="I44" s="171" t="n"/>
+      <c r="J44" s="171" t="n"/>
+      <c r="K44" s="171" t="n"/>
+      <c r="L44" s="171" t="n"/>
+      <c r="M44" s="171" t="n"/>
+      <c r="P44" s="166" t="inlineStr">
         <is>
           <t>POLLINI NON IDENTIFICATI</t>
         </is>
       </c>
-      <c r="Q44" s="46" t="n"/>
-      <c r="R44" s="47" t="n"/>
-      <c r="S44" s="55">
+      <c r="Q44" s="169" t="n"/>
+      <c r="R44" s="169" t="n"/>
+      <c r="S44" s="173">
         <f>G44*$Q$3</f>
         <v/>
       </c>
-      <c r="T44" s="55">
+      <c r="T44" s="173">
         <f>H44*$Q$3</f>
         <v/>
       </c>
-      <c r="U44" s="55">
+      <c r="U44" s="173">
         <f>I44*$Q$3</f>
         <v/>
       </c>
-      <c r="V44" s="55">
+      <c r="V44" s="173">
         <f>J44*$Q$3</f>
         <v/>
       </c>
-      <c r="W44" s="55">
+      <c r="W44" s="173">
         <f>K44*$Q$3</f>
         <v/>
       </c>
-      <c r="X44" s="55">
+      <c r="X44" s="173">
         <f>L44*$Q$3</f>
         <v/>
       </c>
@@ -3891,48 +4266,48 @@
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="40">
-      <c r="D45" s="51" t="inlineStr">
+      <c r="D45" s="168" t="inlineStr">
         <is>
           <t>POLYGONACEAE</t>
         </is>
       </c>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="47" t="n"/>
-      <c r="G45" s="53" t="n"/>
-      <c r="H45" s="53" t="n"/>
-      <c r="I45" s="53" t="n"/>
-      <c r="J45" s="53" t="n"/>
-      <c r="K45" s="53" t="n"/>
-      <c r="L45" s="53" t="n"/>
-      <c r="M45" s="53" t="n"/>
-      <c r="P45" s="54" t="inlineStr">
+      <c r="E45" s="169" t="n"/>
+      <c r="F45" s="169" t="n"/>
+      <c r="G45" s="171" t="n"/>
+      <c r="H45" s="171" t="n"/>
+      <c r="I45" s="171" t="n"/>
+      <c r="J45" s="171" t="n"/>
+      <c r="K45" s="171" t="n"/>
+      <c r="L45" s="171" t="n"/>
+      <c r="M45" s="171" t="n"/>
+      <c r="P45" s="172" t="inlineStr">
         <is>
           <t>POLYGONACEAE</t>
         </is>
       </c>
-      <c r="Q45" s="46" t="n"/>
-      <c r="R45" s="47" t="n"/>
-      <c r="S45" s="55">
+      <c r="Q45" s="169" t="n"/>
+      <c r="R45" s="169" t="n"/>
+      <c r="S45" s="173">
         <f>G45*$Q$3</f>
         <v/>
       </c>
-      <c r="T45" s="55">
+      <c r="T45" s="173">
         <f>H45*$Q$3</f>
         <v/>
       </c>
-      <c r="U45" s="55">
+      <c r="U45" s="173">
         <f>I45*$Q$3</f>
         <v/>
       </c>
-      <c r="V45" s="55">
+      <c r="V45" s="173">
         <f>J45*$Q$3</f>
         <v/>
       </c>
-      <c r="W45" s="55">
+      <c r="W45" s="173">
         <f>K45*$Q$3</f>
         <v/>
       </c>
-      <c r="X45" s="55">
+      <c r="X45" s="173">
         <f>L45*$Q$3</f>
         <v/>
       </c>
@@ -3946,48 +4321,48 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="40">
-      <c r="D46" s="58" t="inlineStr">
+      <c r="D46" s="174" t="inlineStr">
         <is>
           <t>SALICACEAE</t>
         </is>
       </c>
-      <c r="E46" s="46" t="n"/>
-      <c r="F46" s="47" t="n"/>
-      <c r="G46" s="53" t="n"/>
-      <c r="H46" s="53" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="53" t="n"/>
-      <c r="K46" s="53" t="n"/>
-      <c r="L46" s="53" t="n"/>
-      <c r="M46" s="53" t="n"/>
-      <c r="P46" s="59" t="inlineStr">
+      <c r="E46" s="169" t="n"/>
+      <c r="F46" s="169" t="n"/>
+      <c r="G46" s="171" t="n"/>
+      <c r="H46" s="171" t="n"/>
+      <c r="I46" s="171" t="n"/>
+      <c r="J46" s="171" t="n"/>
+      <c r="K46" s="171" t="n"/>
+      <c r="L46" s="171" t="n"/>
+      <c r="M46" s="171" t="n"/>
+      <c r="P46" s="166" t="inlineStr">
         <is>
           <t>SALICACEAE</t>
         </is>
       </c>
-      <c r="Q46" s="46" t="n"/>
-      <c r="R46" s="47" t="n"/>
-      <c r="S46" s="55">
+      <c r="Q46" s="169" t="n"/>
+      <c r="R46" s="169" t="n"/>
+      <c r="S46" s="173">
         <f>G46*$Q$3</f>
         <v/>
       </c>
-      <c r="T46" s="55">
+      <c r="T46" s="173">
         <f>H46*$Q$3</f>
         <v/>
       </c>
-      <c r="U46" s="55">
+      <c r="U46" s="173">
         <f>I46*$Q$3</f>
         <v/>
       </c>
-      <c r="V46" s="55">
+      <c r="V46" s="173">
         <f>J46*$Q$3</f>
         <v/>
       </c>
-      <c r="W46" s="55">
+      <c r="W46" s="173">
         <f>K46*$Q$3</f>
         <v/>
       </c>
-      <c r="X46" s="55">
+      <c r="X46" s="173">
         <f>L46*$Q$3</f>
         <v/>
       </c>
@@ -4001,48 +4376,48 @@
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="40">
-      <c r="D47" s="58" t="inlineStr">
+      <c r="D47" s="174" t="inlineStr">
         <is>
           <t>Populus</t>
         </is>
       </c>
-      <c r="E47" s="46" t="n"/>
-      <c r="F47" s="47" t="n"/>
-      <c r="G47" s="53" t="n"/>
-      <c r="H47" s="53" t="n"/>
-      <c r="I47" s="53" t="n"/>
-      <c r="J47" s="53" t="n"/>
-      <c r="K47" s="53" t="n"/>
-      <c r="L47" s="53" t="n"/>
-      <c r="M47" s="53" t="n"/>
-      <c r="P47" s="59" t="inlineStr">
+      <c r="E47" s="169" t="n"/>
+      <c r="F47" s="169" t="n"/>
+      <c r="G47" s="171" t="n"/>
+      <c r="H47" s="171" t="n"/>
+      <c r="I47" s="171" t="n"/>
+      <c r="J47" s="171" t="n"/>
+      <c r="K47" s="171" t="n"/>
+      <c r="L47" s="171" t="n"/>
+      <c r="M47" s="171" t="n"/>
+      <c r="P47" s="166" t="inlineStr">
         <is>
           <t>Populus</t>
         </is>
       </c>
-      <c r="Q47" s="46" t="n"/>
-      <c r="R47" s="47" t="n"/>
-      <c r="S47" s="55">
+      <c r="Q47" s="169" t="n"/>
+      <c r="R47" s="169" t="n"/>
+      <c r="S47" s="173">
         <f>G47*$Q$3</f>
         <v/>
       </c>
-      <c r="T47" s="55">
+      <c r="T47" s="173">
         <f>H47*$Q$3</f>
         <v/>
       </c>
-      <c r="U47" s="55">
+      <c r="U47" s="173">
         <f>I47*$Q$3</f>
         <v/>
       </c>
-      <c r="V47" s="55">
+      <c r="V47" s="173">
         <f>J47*$Q$3</f>
         <v/>
       </c>
-      <c r="W47" s="55">
+      <c r="W47" s="173">
         <f>K47*$Q$3</f>
         <v/>
       </c>
-      <c r="X47" s="55">
+      <c r="X47" s="173">
         <f>L47*$Q$3</f>
         <v/>
       </c>
@@ -4056,48 +4431,48 @@
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="40">
-      <c r="D48" s="58" t="inlineStr">
+      <c r="D48" s="174" t="inlineStr">
         <is>
           <t>Salix</t>
         </is>
       </c>
-      <c r="E48" s="46" t="n"/>
-      <c r="F48" s="47" t="n"/>
-      <c r="G48" s="53" t="n"/>
-      <c r="H48" s="53" t="n"/>
-      <c r="I48" s="53" t="n"/>
-      <c r="J48" s="53" t="n"/>
-      <c r="K48" s="53" t="n"/>
-      <c r="L48" s="53" t="n"/>
-      <c r="M48" s="53" t="n"/>
-      <c r="P48" s="59" t="inlineStr">
+      <c r="E48" s="169" t="n"/>
+      <c r="F48" s="169" t="n"/>
+      <c r="G48" s="171" t="n"/>
+      <c r="H48" s="171" t="n"/>
+      <c r="I48" s="171" t="n"/>
+      <c r="J48" s="171" t="n"/>
+      <c r="K48" s="171" t="n"/>
+      <c r="L48" s="171" t="n"/>
+      <c r="M48" s="171" t="n"/>
+      <c r="P48" s="166" t="inlineStr">
         <is>
           <t>Salix</t>
         </is>
       </c>
-      <c r="Q48" s="46" t="n"/>
-      <c r="R48" s="47" t="n"/>
-      <c r="S48" s="55">
+      <c r="Q48" s="169" t="n"/>
+      <c r="R48" s="169" t="n"/>
+      <c r="S48" s="173">
         <f>G48*$Q$3</f>
         <v/>
       </c>
-      <c r="T48" s="55">
+      <c r="T48" s="173">
         <f>H48*$Q$3</f>
         <v/>
       </c>
-      <c r="U48" s="55">
+      <c r="U48" s="173">
         <f>I48*$Q$3</f>
         <v/>
       </c>
-      <c r="V48" s="55">
+      <c r="V48" s="173">
         <f>J48*$Q$3</f>
         <v/>
       </c>
-      <c r="W48" s="55">
+      <c r="W48" s="173">
         <f>K48*$Q$3</f>
         <v/>
       </c>
-      <c r="X48" s="55">
+      <c r="X48" s="173">
         <f>L48*$Q$3</f>
         <v/>
       </c>
@@ -4111,48 +4486,48 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="40">
-      <c r="D49" s="51" t="inlineStr">
+      <c r="D49" s="168" t="inlineStr">
         <is>
           <t>TILIACEAE</t>
         </is>
       </c>
-      <c r="E49" s="46" t="n"/>
-      <c r="F49" s="47" t="n"/>
-      <c r="G49" s="53" t="n"/>
-      <c r="H49" s="53" t="n"/>
-      <c r="I49" s="53" t="n"/>
-      <c r="J49" s="53" t="n"/>
-      <c r="K49" s="53" t="n"/>
-      <c r="L49" s="53" t="n"/>
-      <c r="M49" s="53" t="n"/>
-      <c r="P49" s="54" t="inlineStr">
+      <c r="E49" s="169" t="n"/>
+      <c r="F49" s="169" t="n"/>
+      <c r="G49" s="171" t="n"/>
+      <c r="H49" s="171" t="n"/>
+      <c r="I49" s="171" t="n"/>
+      <c r="J49" s="171" t="n"/>
+      <c r="K49" s="171" t="n"/>
+      <c r="L49" s="171" t="n"/>
+      <c r="M49" s="171" t="n"/>
+      <c r="P49" s="172" t="inlineStr">
         <is>
           <t>TILIACEAE</t>
         </is>
       </c>
-      <c r="Q49" s="46" t="n"/>
-      <c r="R49" s="47" t="n"/>
-      <c r="S49" s="55">
+      <c r="Q49" s="169" t="n"/>
+      <c r="R49" s="169" t="n"/>
+      <c r="S49" s="173">
         <f>G49*$Q$3</f>
         <v/>
       </c>
-      <c r="T49" s="55">
+      <c r="T49" s="173">
         <f>H49*$Q$3</f>
         <v/>
       </c>
-      <c r="U49" s="55">
+      <c r="U49" s="173">
         <f>I49*$Q$3</f>
         <v/>
       </c>
-      <c r="V49" s="55">
+      <c r="V49" s="173">
         <f>J49*$Q$3</f>
         <v/>
       </c>
-      <c r="W49" s="55">
+      <c r="W49" s="173">
         <f>K49*$Q$3</f>
         <v/>
       </c>
-      <c r="X49" s="55">
+      <c r="X49" s="173">
         <f>L49*$Q$3</f>
         <v/>
       </c>
@@ -4166,48 +4541,48 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="40">
-      <c r="D50" s="51" t="inlineStr">
+      <c r="D50" s="168" t="inlineStr">
         <is>
           <t>ULMACEAE</t>
         </is>
       </c>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="47" t="n"/>
-      <c r="G50" s="53" t="n"/>
-      <c r="H50" s="53" t="n"/>
-      <c r="I50" s="53" t="n"/>
-      <c r="J50" s="53" t="n"/>
-      <c r="K50" s="53" t="n"/>
-      <c r="L50" s="53" t="n"/>
-      <c r="M50" s="53" t="n"/>
-      <c r="P50" s="54" t="inlineStr">
+      <c r="E50" s="169" t="n"/>
+      <c r="F50" s="169" t="n"/>
+      <c r="G50" s="171" t="n"/>
+      <c r="H50" s="171" t="n"/>
+      <c r="I50" s="171" t="n"/>
+      <c r="J50" s="171" t="n"/>
+      <c r="K50" s="171" t="n"/>
+      <c r="L50" s="171" t="n"/>
+      <c r="M50" s="171" t="n"/>
+      <c r="P50" s="172" t="inlineStr">
         <is>
           <t>ULMACEAE</t>
         </is>
       </c>
-      <c r="Q50" s="46" t="n"/>
-      <c r="R50" s="47" t="n"/>
-      <c r="S50" s="55">
+      <c r="Q50" s="169" t="n"/>
+      <c r="R50" s="169" t="n"/>
+      <c r="S50" s="173">
         <f>G50*$Q$3</f>
         <v/>
       </c>
-      <c r="T50" s="55">
+      <c r="T50" s="173">
         <f>H50*$Q$3</f>
         <v/>
       </c>
-      <c r="U50" s="55">
+      <c r="U50" s="173">
         <f>I50*$Q$3</f>
         <v/>
       </c>
-      <c r="V50" s="55">
+      <c r="V50" s="173">
         <f>J50*$Q$3</f>
         <v/>
       </c>
-      <c r="W50" s="55">
+      <c r="W50" s="173">
         <f>K50*$Q$3</f>
         <v/>
       </c>
-      <c r="X50" s="55">
+      <c r="X50" s="173">
         <f>L50*$Q$3</f>
         <v/>
       </c>
@@ -4221,48 +4596,48 @@
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="40">
-      <c r="D51" s="51" t="inlineStr">
+      <c r="D51" s="168" t="inlineStr">
         <is>
           <t>UMBELLIFERAE</t>
         </is>
       </c>
-      <c r="E51" s="46" t="n"/>
-      <c r="F51" s="47" t="n"/>
-      <c r="G51" s="53" t="n"/>
-      <c r="H51" s="53" t="n"/>
-      <c r="I51" s="53" t="n"/>
-      <c r="J51" s="53" t="n"/>
-      <c r="K51" s="53" t="n"/>
-      <c r="L51" s="53" t="n"/>
-      <c r="M51" s="53" t="n"/>
-      <c r="P51" s="54" t="inlineStr">
+      <c r="E51" s="169" t="n"/>
+      <c r="F51" s="169" t="n"/>
+      <c r="G51" s="171" t="n"/>
+      <c r="H51" s="171" t="n"/>
+      <c r="I51" s="171" t="n"/>
+      <c r="J51" s="171" t="n"/>
+      <c r="K51" s="171" t="n"/>
+      <c r="L51" s="171" t="n"/>
+      <c r="M51" s="171" t="n"/>
+      <c r="P51" s="172" t="inlineStr">
         <is>
           <t>UMBELLIFERAE</t>
         </is>
       </c>
-      <c r="Q51" s="46" t="n"/>
-      <c r="R51" s="47" t="n"/>
-      <c r="S51" s="55">
+      <c r="Q51" s="169" t="n"/>
+      <c r="R51" s="169" t="n"/>
+      <c r="S51" s="173">
         <f>G51*$Q$3</f>
         <v/>
       </c>
-      <c r="T51" s="55">
+      <c r="T51" s="173">
         <f>H51*$Q$3</f>
         <v/>
       </c>
-      <c r="U51" s="55">
+      <c r="U51" s="173">
         <f>I51*$Q$3</f>
         <v/>
       </c>
-      <c r="V51" s="55">
+      <c r="V51" s="173">
         <f>J51*$Q$3</f>
         <v/>
       </c>
-      <c r="W51" s="55">
+      <c r="W51" s="173">
         <f>K51*$Q$3</f>
         <v/>
       </c>
-      <c r="X51" s="55">
+      <c r="X51" s="173">
         <f>L51*$Q$3</f>
         <v/>
       </c>
@@ -4276,48 +4651,48 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="40">
-      <c r="D52" s="60" t="inlineStr">
+      <c r="D52" s="175" t="inlineStr">
         <is>
           <t>URTICACEAE</t>
         </is>
       </c>
-      <c r="E52" s="46" t="n"/>
-      <c r="F52" s="47" t="n"/>
-      <c r="G52" s="61" t="n"/>
-      <c r="H52" s="61" t="n"/>
-      <c r="I52" s="61" t="n"/>
-      <c r="J52" s="61" t="n"/>
-      <c r="K52" s="61" t="n"/>
-      <c r="L52" s="61" t="n"/>
-      <c r="M52" s="61" t="n"/>
-      <c r="P52" s="62" t="inlineStr">
+      <c r="E52" s="169" t="n"/>
+      <c r="F52" s="169" t="n"/>
+      <c r="G52" s="176" t="n"/>
+      <c r="H52" s="176" t="n"/>
+      <c r="I52" s="176" t="n"/>
+      <c r="J52" s="176" t="n"/>
+      <c r="K52" s="176" t="n"/>
+      <c r="L52" s="176" t="n"/>
+      <c r="M52" s="176" t="n"/>
+      <c r="P52" s="177" t="inlineStr">
         <is>
           <t>URTICACEAE</t>
         </is>
       </c>
-      <c r="Q52" s="46" t="n"/>
-      <c r="R52" s="47" t="n"/>
-      <c r="S52" s="63">
+      <c r="Q52" s="169" t="n"/>
+      <c r="R52" s="169" t="n"/>
+      <c r="S52" s="178">
         <f>G52*$Q$3</f>
         <v/>
       </c>
-      <c r="T52" s="63">
+      <c r="T52" s="178">
         <f>H52*$Q$3</f>
         <v/>
       </c>
-      <c r="U52" s="63">
+      <c r="U52" s="178">
         <f>I52*$Q$3</f>
         <v/>
       </c>
-      <c r="V52" s="63">
+      <c r="V52" s="178">
         <f>J52*$Q$3</f>
         <v/>
       </c>
-      <c r="W52" s="63">
+      <c r="W52" s="178">
         <f>K52*$Q$3</f>
         <v/>
       </c>
-      <c r="X52" s="63">
+      <c r="X52" s="178">
         <f>L52*$Q$3</f>
         <v/>
       </c>
@@ -4331,69 +4706,69 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="40">
-      <c r="D53" s="58" t="inlineStr">
+      <c r="D53" s="174" t="inlineStr">
         <is>
           <t>Totali</t>
         </is>
       </c>
-      <c r="E53" s="46" t="n"/>
-      <c r="F53" s="47" t="n"/>
-      <c r="G53" s="58">
+      <c r="E53" s="166" t="n"/>
+      <c r="F53" s="166" t="n"/>
+      <c r="G53" s="174">
         <f>SUM(G6:G52)</f>
         <v/>
       </c>
-      <c r="H53" s="58">
+      <c r="H53" s="174">
         <f>SUM(H6:H52)</f>
         <v/>
       </c>
-      <c r="I53" s="58">
+      <c r="I53" s="174">
         <f>SUM(I6:I52)</f>
         <v/>
       </c>
-      <c r="J53" s="58">
+      <c r="J53" s="174">
         <f>SUM(J6:J52)</f>
         <v/>
       </c>
-      <c r="K53" s="58">
+      <c r="K53" s="174">
         <f>SUM(K6:K52)</f>
         <v/>
       </c>
-      <c r="L53" s="58">
+      <c r="L53" s="174">
         <f>SUM(L6:L52)</f>
         <v/>
       </c>
-      <c r="M53" s="58">
+      <c r="M53" s="174">
         <f>SUM(M6:M52)</f>
         <v/>
       </c>
-      <c r="P53" s="58" t="inlineStr">
+      <c r="P53" s="174" t="inlineStr">
         <is>
           <t>Totali</t>
         </is>
       </c>
-      <c r="Q53" s="46" t="n"/>
-      <c r="R53" s="47" t="n"/>
-      <c r="S53" s="58">
+      <c r="Q53" s="166" t="n"/>
+      <c r="R53" s="166" t="n"/>
+      <c r="S53" s="174">
         <f>SUM(S6:S52)</f>
         <v/>
       </c>
-      <c r="T53" s="58">
+      <c r="T53" s="174">
         <f>SUM(T6:T52)</f>
         <v/>
       </c>
-      <c r="U53" s="58">
+      <c r="U53" s="174">
         <f>SUM(U6:U52)</f>
         <v/>
       </c>
-      <c r="V53" s="58">
+      <c r="V53" s="174">
         <f>SUM(V6:V52)</f>
         <v/>
       </c>
-      <c r="W53" s="58">
+      <c r="W53" s="174">
         <f>SUM(W6:W52)</f>
         <v/>
       </c>
-      <c r="X53" s="58">
+      <c r="X53" s="174">
         <f>SUM(X6:X52)</f>
         <v/>
       </c>
@@ -4407,81 +4782,81 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="40">
-      <c r="D57" s="45" t="inlineStr">
+      <c r="D57" s="165" t="inlineStr">
         <is>
           <t>SPORE</t>
         </is>
       </c>
-      <c r="E57" s="46" t="n"/>
-      <c r="F57" s="47" t="n"/>
-      <c r="G57" s="45" t="inlineStr">
+      <c r="E57" s="166" t="n"/>
+      <c r="F57" s="166" t="n"/>
+      <c r="G57" s="165" t="inlineStr">
         <is>
           <t>LUNEDI</t>
         </is>
       </c>
-      <c r="H57" s="45" t="inlineStr">
+      <c r="H57" s="165" t="inlineStr">
         <is>
           <t>MARTEDI</t>
         </is>
       </c>
-      <c r="I57" s="45" t="inlineStr">
+      <c r="I57" s="165" t="inlineStr">
         <is>
           <t>MERC.</t>
         </is>
       </c>
-      <c r="J57" s="45" t="inlineStr">
+      <c r="J57" s="165" t="inlineStr">
         <is>
           <t>GIOVEDI</t>
         </is>
       </c>
-      <c r="K57" s="45" t="inlineStr">
+      <c r="K57" s="165" t="inlineStr">
         <is>
           <t>VENERDI</t>
         </is>
       </c>
-      <c r="L57" s="45" t="inlineStr">
+      <c r="L57" s="165" t="inlineStr">
         <is>
           <t>SABATO</t>
         </is>
       </c>
-      <c r="M57" s="45" t="inlineStr">
+      <c r="M57" s="165" t="inlineStr">
         <is>
           <t>DOMEN.</t>
         </is>
       </c>
-      <c r="P57" s="48" t="inlineStr">
+      <c r="P57" s="167" t="inlineStr">
         <is>
           <t>SPORE</t>
         </is>
       </c>
-      <c r="Q57" s="46" t="n"/>
-      <c r="R57" s="47" t="n"/>
-      <c r="S57" s="45" t="inlineStr">
+      <c r="Q57" s="166" t="n"/>
+      <c r="R57" s="166" t="n"/>
+      <c r="S57" s="165" t="inlineStr">
         <is>
           <t>LUNEDI</t>
         </is>
       </c>
-      <c r="T57" s="45" t="inlineStr">
+      <c r="T57" s="165" t="inlineStr">
         <is>
           <t>MARTEDI</t>
         </is>
       </c>
-      <c r="U57" s="45" t="inlineStr">
+      <c r="U57" s="165" t="inlineStr">
         <is>
           <t>MERC.</t>
         </is>
       </c>
-      <c r="V57" s="45" t="inlineStr">
+      <c r="V57" s="165" t="inlineStr">
         <is>
           <t>GIOVEDI</t>
         </is>
       </c>
-      <c r="W57" s="45" t="inlineStr">
+      <c r="W57" s="165" t="inlineStr">
         <is>
           <t>VENERDI</t>
         </is>
       </c>
-      <c r="X57" s="45" t="inlineStr">
+      <c r="X57" s="165" t="inlineStr">
         <is>
           <t>SABATO</t>
         </is>
@@ -4498,48 +4873,48 @@
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="40">
-      <c r="D58" s="69" t="inlineStr">
+      <c r="D58" s="181" t="inlineStr">
         <is>
           <t>Alternaria</t>
         </is>
       </c>
-      <c r="E58" s="46" t="n"/>
-      <c r="F58" s="47" t="n"/>
-      <c r="G58" s="61" t="n"/>
-      <c r="H58" s="61" t="n"/>
-      <c r="I58" s="61" t="n"/>
-      <c r="J58" s="61" t="n"/>
-      <c r="K58" s="61" t="n"/>
-      <c r="L58" s="61" t="n"/>
-      <c r="M58" s="61" t="n"/>
-      <c r="P58" s="70" t="inlineStr">
+      <c r="E58" s="169" t="n"/>
+      <c r="F58" s="169" t="n"/>
+      <c r="G58" s="176" t="n"/>
+      <c r="H58" s="176" t="n"/>
+      <c r="I58" s="176" t="n"/>
+      <c r="J58" s="176" t="n"/>
+      <c r="K58" s="176" t="n"/>
+      <c r="L58" s="176" t="n"/>
+      <c r="M58" s="176" t="n"/>
+      <c r="P58" s="182" t="inlineStr">
         <is>
           <t>Alternaria</t>
         </is>
       </c>
-      <c r="Q58" s="46" t="n"/>
-      <c r="R58" s="47" t="n"/>
-      <c r="S58" s="63">
+      <c r="Q58" s="169" t="n"/>
+      <c r="R58" s="169" t="n"/>
+      <c r="S58" s="178">
         <f>G58*$Q$3</f>
         <v/>
       </c>
-      <c r="T58" s="63">
+      <c r="T58" s="178">
         <f>H58*$Q$3</f>
         <v/>
       </c>
-      <c r="U58" s="63">
+      <c r="U58" s="178">
         <f>I58*$Q$3</f>
         <v/>
       </c>
-      <c r="V58" s="63">
+      <c r="V58" s="178">
         <f>J58*$Q$3</f>
         <v/>
       </c>
-      <c r="W58" s="63">
+      <c r="W58" s="178">
         <f>K58*$Q$3</f>
         <v/>
       </c>
-      <c r="X58" s="63">
+      <c r="X58" s="178">
         <f>L58*$Q$3</f>
         <v/>
       </c>
@@ -4553,48 +4928,48 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="40">
-      <c r="D59" s="51" t="inlineStr">
+      <c r="D59" s="168" t="inlineStr">
         <is>
           <t>Botrytis</t>
         </is>
       </c>
-      <c r="E59" s="46" t="n"/>
-      <c r="F59" s="47" t="n"/>
-      <c r="G59" s="53" t="n"/>
-      <c r="H59" s="53" t="n"/>
-      <c r="I59" s="53" t="n"/>
-      <c r="J59" s="53" t="n"/>
-      <c r="K59" s="53" t="n"/>
-      <c r="L59" s="53" t="n"/>
-      <c r="M59" s="53" t="n"/>
-      <c r="P59" s="54" t="inlineStr">
+      <c r="E59" s="169" t="n"/>
+      <c r="F59" s="169" t="n"/>
+      <c r="G59" s="171" t="n"/>
+      <c r="H59" s="171" t="n"/>
+      <c r="I59" s="171" t="n"/>
+      <c r="J59" s="171" t="n"/>
+      <c r="K59" s="171" t="n"/>
+      <c r="L59" s="171" t="n"/>
+      <c r="M59" s="171" t="n"/>
+      <c r="P59" s="172" t="inlineStr">
         <is>
           <t>Botrytis</t>
         </is>
       </c>
-      <c r="Q59" s="46" t="n"/>
-      <c r="R59" s="47" t="n"/>
-      <c r="S59" s="55">
+      <c r="Q59" s="169" t="n"/>
+      <c r="R59" s="169" t="n"/>
+      <c r="S59" s="173">
         <f>G59*$Q$3</f>
         <v/>
       </c>
-      <c r="T59" s="55">
+      <c r="T59" s="173">
         <f>H59*$Q$3</f>
         <v/>
       </c>
-      <c r="U59" s="55">
+      <c r="U59" s="173">
         <f>I59*$Q$3</f>
         <v/>
       </c>
-      <c r="V59" s="55">
+      <c r="V59" s="173">
         <f>J59*$Q$3</f>
         <v/>
       </c>
-      <c r="W59" s="55">
+      <c r="W59" s="173">
         <f>K59*$Q$3</f>
         <v/>
       </c>
-      <c r="X59" s="55">
+      <c r="X59" s="173">
         <f>L59*$Q$3</f>
         <v/>
       </c>
@@ -4608,48 +4983,48 @@
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="40">
-      <c r="D60" s="51" t="inlineStr">
+      <c r="D60" s="168" t="inlineStr">
         <is>
           <t>Cladosporium</t>
         </is>
       </c>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="47" t="n"/>
-      <c r="G60" s="53" t="n"/>
-      <c r="H60" s="53" t="n"/>
-      <c r="I60" s="53" t="n"/>
-      <c r="J60" s="53" t="n"/>
-      <c r="K60" s="53" t="n"/>
-      <c r="L60" s="53" t="n"/>
-      <c r="M60" s="53" t="n"/>
-      <c r="P60" s="54" t="inlineStr">
+      <c r="E60" s="169" t="n"/>
+      <c r="F60" s="169" t="n"/>
+      <c r="G60" s="171" t="n"/>
+      <c r="H60" s="171" t="n"/>
+      <c r="I60" s="171" t="n"/>
+      <c r="J60" s="171" t="n"/>
+      <c r="K60" s="171" t="n"/>
+      <c r="L60" s="171" t="n"/>
+      <c r="M60" s="171" t="n"/>
+      <c r="P60" s="172" t="inlineStr">
         <is>
           <t>Cladosporium</t>
         </is>
       </c>
-      <c r="Q60" s="46" t="n"/>
-      <c r="R60" s="47" t="n"/>
-      <c r="S60" s="55">
+      <c r="Q60" s="169" t="n"/>
+      <c r="R60" s="169" t="n"/>
+      <c r="S60" s="173">
         <f>G60*$Q$3</f>
         <v/>
       </c>
-      <c r="T60" s="55">
+      <c r="T60" s="173">
         <f>H60*$Q$3</f>
         <v/>
       </c>
-      <c r="U60" s="55">
+      <c r="U60" s="173">
         <f>I60*$Q$3</f>
         <v/>
       </c>
-      <c r="V60" s="55">
+      <c r="V60" s="173">
         <f>J60*$Q$3</f>
         <v/>
       </c>
-      <c r="W60" s="55">
+      <c r="W60" s="173">
         <f>K60*$Q$3</f>
         <v/>
       </c>
-      <c r="X60" s="55">
+      <c r="X60" s="173">
         <f>L60*$Q$3</f>
         <v/>
       </c>
@@ -4663,48 +5038,48 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="40">
-      <c r="D61" s="51" t="inlineStr">
+      <c r="D61" s="168" t="inlineStr">
         <is>
           <t>Curvularia</t>
         </is>
       </c>
-      <c r="E61" s="46" t="n"/>
-      <c r="F61" s="47" t="n"/>
-      <c r="G61" s="53" t="n"/>
-      <c r="H61" s="53" t="n"/>
-      <c r="I61" s="53" t="n"/>
-      <c r="J61" s="53" t="n"/>
-      <c r="K61" s="53" t="n"/>
-      <c r="L61" s="53" t="n"/>
-      <c r="M61" s="53" t="n"/>
-      <c r="P61" s="54" t="inlineStr">
+      <c r="E61" s="169" t="n"/>
+      <c r="F61" s="169" t="n"/>
+      <c r="G61" s="171" t="n"/>
+      <c r="H61" s="171" t="n"/>
+      <c r="I61" s="171" t="n"/>
+      <c r="J61" s="171" t="n"/>
+      <c r="K61" s="171" t="n"/>
+      <c r="L61" s="171" t="n"/>
+      <c r="M61" s="171" t="n"/>
+      <c r="P61" s="172" t="inlineStr">
         <is>
           <t>Curvularia</t>
         </is>
       </c>
-      <c r="Q61" s="46" t="n"/>
-      <c r="R61" s="47" t="n"/>
-      <c r="S61" s="55">
+      <c r="Q61" s="169" t="n"/>
+      <c r="R61" s="169" t="n"/>
+      <c r="S61" s="173">
         <f>G61*$Q$3</f>
         <v/>
       </c>
-      <c r="T61" s="55">
+      <c r="T61" s="173">
         <f>H61*$Q$3</f>
         <v/>
       </c>
-      <c r="U61" s="55">
+      <c r="U61" s="173">
         <f>I61*$Q$3</f>
         <v/>
       </c>
-      <c r="V61" s="55">
+      <c r="V61" s="173">
         <f>J61*$Q$3</f>
         <v/>
       </c>
-      <c r="W61" s="55">
+      <c r="W61" s="173">
         <f>K61*$Q$3</f>
         <v/>
       </c>
-      <c r="X61" s="55">
+      <c r="X61" s="173">
         <f>L61*$Q$3</f>
         <v/>
       </c>
@@ -4718,48 +5093,48 @@
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="40">
-      <c r="D62" s="51" t="inlineStr">
+      <c r="D62" s="168" t="inlineStr">
         <is>
           <t>Epicoccum</t>
         </is>
       </c>
-      <c r="E62" s="46" t="n"/>
-      <c r="F62" s="47" t="n"/>
-      <c r="G62" s="53" t="n"/>
-      <c r="H62" s="53" t="n"/>
-      <c r="I62" s="53" t="n"/>
-      <c r="J62" s="53" t="n"/>
-      <c r="K62" s="53" t="n"/>
-      <c r="L62" s="53" t="n"/>
-      <c r="M62" s="53" t="n"/>
-      <c r="P62" s="54" t="inlineStr">
+      <c r="E62" s="169" t="n"/>
+      <c r="F62" s="169" t="n"/>
+      <c r="G62" s="171" t="n"/>
+      <c r="H62" s="171" t="n"/>
+      <c r="I62" s="171" t="n"/>
+      <c r="J62" s="171" t="n"/>
+      <c r="K62" s="171" t="n"/>
+      <c r="L62" s="171" t="n"/>
+      <c r="M62" s="171" t="n"/>
+      <c r="P62" s="172" t="inlineStr">
         <is>
           <t>Epicoccum</t>
         </is>
       </c>
-      <c r="Q62" s="46" t="n"/>
-      <c r="R62" s="47" t="n"/>
-      <c r="S62" s="55">
+      <c r="Q62" s="169" t="n"/>
+      <c r="R62" s="169" t="n"/>
+      <c r="S62" s="173">
         <f>G62*$Q$3</f>
         <v/>
       </c>
-      <c r="T62" s="55">
+      <c r="T62" s="173">
         <f>H62*$Q$3</f>
         <v/>
       </c>
-      <c r="U62" s="55">
+      <c r="U62" s="173">
         <f>I62*$Q$3</f>
         <v/>
       </c>
-      <c r="V62" s="55">
+      <c r="V62" s="173">
         <f>J62*$Q$3</f>
         <v/>
       </c>
-      <c r="W62" s="55">
+      <c r="W62" s="173">
         <f>K62*$Q$3</f>
         <v/>
       </c>
-      <c r="X62" s="55">
+      <c r="X62" s="173">
         <f>L62*$Q$3</f>
         <v/>
       </c>
@@ -4773,48 +5148,48 @@
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="40">
-      <c r="D63" s="51" t="inlineStr">
+      <c r="D63" s="168" t="inlineStr">
         <is>
           <t>Helminthosporium</t>
         </is>
       </c>
-      <c r="E63" s="46" t="n"/>
-      <c r="F63" s="47" t="n"/>
-      <c r="G63" s="53" t="n"/>
-      <c r="H63" s="53" t="n"/>
-      <c r="I63" s="53" t="n"/>
-      <c r="J63" s="53" t="n"/>
-      <c r="K63" s="53" t="n"/>
-      <c r="L63" s="53" t="n"/>
-      <c r="M63" s="53" t="n"/>
-      <c r="P63" s="54" t="inlineStr">
+      <c r="E63" s="169" t="n"/>
+      <c r="F63" s="169" t="n"/>
+      <c r="G63" s="171" t="n"/>
+      <c r="H63" s="171" t="n"/>
+      <c r="I63" s="171" t="n"/>
+      <c r="J63" s="171" t="n"/>
+      <c r="K63" s="171" t="n"/>
+      <c r="L63" s="171" t="n"/>
+      <c r="M63" s="171" t="n"/>
+      <c r="P63" s="172" t="inlineStr">
         <is>
           <t>Helminthosporium</t>
         </is>
       </c>
-      <c r="Q63" s="46" t="n"/>
-      <c r="R63" s="47" t="n"/>
-      <c r="S63" s="55">
+      <c r="Q63" s="169" t="n"/>
+      <c r="R63" s="169" t="n"/>
+      <c r="S63" s="173">
         <f>G63*$Q$3</f>
         <v/>
       </c>
-      <c r="T63" s="55">
+      <c r="T63" s="173">
         <f>H63*$Q$3</f>
         <v/>
       </c>
-      <c r="U63" s="55">
+      <c r="U63" s="173">
         <f>I63*$Q$3</f>
         <v/>
       </c>
-      <c r="V63" s="55">
+      <c r="V63" s="173">
         <f>J63*$Q$3</f>
         <v/>
       </c>
-      <c r="W63" s="55">
+      <c r="W63" s="173">
         <f>K63*$Q$3</f>
         <v/>
       </c>
-      <c r="X63" s="55">
+      <c r="X63" s="173">
         <f>L63*$Q$3</f>
         <v/>
       </c>
@@ -4828,48 +5203,48 @@
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="40">
-      <c r="D64" s="51" t="inlineStr">
+      <c r="D64" s="168" t="inlineStr">
         <is>
           <t>Pithomyces</t>
         </is>
       </c>
-      <c r="E64" s="46" t="n"/>
-      <c r="F64" s="47" t="n"/>
-      <c r="G64" s="53" t="n"/>
-      <c r="H64" s="53" t="n"/>
-      <c r="I64" s="53" t="n"/>
-      <c r="J64" s="53" t="n"/>
-      <c r="K64" s="53" t="n"/>
-      <c r="L64" s="53" t="n"/>
-      <c r="M64" s="53" t="n"/>
-      <c r="P64" s="54" t="inlineStr">
+      <c r="E64" s="169" t="n"/>
+      <c r="F64" s="169" t="n"/>
+      <c r="G64" s="171" t="n"/>
+      <c r="H64" s="171" t="n"/>
+      <c r="I64" s="171" t="n"/>
+      <c r="J64" s="171" t="n"/>
+      <c r="K64" s="171" t="n"/>
+      <c r="L64" s="171" t="n"/>
+      <c r="M64" s="171" t="n"/>
+      <c r="P64" s="172" t="inlineStr">
         <is>
           <t>Pithomyces</t>
         </is>
       </c>
-      <c r="Q64" s="46" t="n"/>
-      <c r="R64" s="47" t="n"/>
-      <c r="S64" s="55">
+      <c r="Q64" s="169" t="n"/>
+      <c r="R64" s="169" t="n"/>
+      <c r="S64" s="173">
         <f>G64*$Q$3</f>
         <v/>
       </c>
-      <c r="T64" s="55">
+      <c r="T64" s="173">
         <f>H64*$Q$3</f>
         <v/>
       </c>
-      <c r="U64" s="55">
+      <c r="U64" s="173">
         <f>I64*$Q$3</f>
         <v/>
       </c>
-      <c r="V64" s="55">
+      <c r="V64" s="173">
         <f>J64*$Q$3</f>
         <v/>
       </c>
-      <c r="W64" s="55">
+      <c r="W64" s="173">
         <f>K64*$Q$3</f>
         <v/>
       </c>
-      <c r="X64" s="55">
+      <c r="X64" s="173">
         <f>L64*$Q$3</f>
         <v/>
       </c>
@@ -4883,48 +5258,48 @@
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="40">
-      <c r="D65" s="51" t="inlineStr">
+      <c r="D65" s="168" t="inlineStr">
         <is>
           <t>Pleospora</t>
         </is>
       </c>
-      <c r="E65" s="46" t="n"/>
-      <c r="F65" s="47" t="n"/>
-      <c r="G65" s="53" t="n"/>
-      <c r="H65" s="53" t="n"/>
-      <c r="I65" s="53" t="n"/>
-      <c r="J65" s="53" t="n"/>
-      <c r="K65" s="53" t="n"/>
-      <c r="L65" s="53" t="n"/>
-      <c r="M65" s="53" t="n"/>
-      <c r="P65" s="54" t="inlineStr">
+      <c r="E65" s="169" t="n"/>
+      <c r="F65" s="169" t="n"/>
+      <c r="G65" s="171" t="n"/>
+      <c r="H65" s="171" t="n"/>
+      <c r="I65" s="171" t="n"/>
+      <c r="J65" s="171" t="n"/>
+      <c r="K65" s="171" t="n"/>
+      <c r="L65" s="171" t="n"/>
+      <c r="M65" s="171" t="n"/>
+      <c r="P65" s="172" t="inlineStr">
         <is>
           <t>Pleospora</t>
         </is>
       </c>
-      <c r="Q65" s="46" t="n"/>
-      <c r="R65" s="47" t="n"/>
-      <c r="S65" s="55">
+      <c r="Q65" s="169" t="n"/>
+      <c r="R65" s="169" t="n"/>
+      <c r="S65" s="173">
         <f>G65*$Q$3</f>
         <v/>
       </c>
-      <c r="T65" s="55">
+      <c r="T65" s="173">
         <f>H65*$Q$3</f>
         <v/>
       </c>
-      <c r="U65" s="55">
+      <c r="U65" s="173">
         <f>I65*$Q$3</f>
         <v/>
       </c>
-      <c r="V65" s="55">
+      <c r="V65" s="173">
         <f>J65*$Q$3</f>
         <v/>
       </c>
-      <c r="W65" s="55">
+      <c r="W65" s="173">
         <f>K65*$Q$3</f>
         <v/>
       </c>
-      <c r="X65" s="55">
+      <c r="X65" s="173">
         <f>L65*$Q$3</f>
         <v/>
       </c>
@@ -4938,48 +5313,48 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="40">
-      <c r="D66" s="51" t="inlineStr">
+      <c r="D66" s="168" t="inlineStr">
         <is>
           <t>Polythrincium</t>
         </is>
       </c>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="47" t="n"/>
-      <c r="G66" s="53" t="n"/>
-      <c r="H66" s="53" t="n"/>
-      <c r="I66" s="53" t="n"/>
-      <c r="J66" s="53" t="n"/>
-      <c r="K66" s="53" t="n"/>
-      <c r="L66" s="53" t="n"/>
-      <c r="M66" s="53" t="n"/>
-      <c r="P66" s="54" t="inlineStr">
+      <c r="E66" s="169" t="n"/>
+      <c r="F66" s="169" t="n"/>
+      <c r="G66" s="171" t="n"/>
+      <c r="H66" s="171" t="n"/>
+      <c r="I66" s="171" t="n"/>
+      <c r="J66" s="171" t="n"/>
+      <c r="K66" s="171" t="n"/>
+      <c r="L66" s="171" t="n"/>
+      <c r="M66" s="171" t="n"/>
+      <c r="P66" s="172" t="inlineStr">
         <is>
           <t>Polythrincium</t>
         </is>
       </c>
-      <c r="Q66" s="46" t="n"/>
-      <c r="R66" s="47" t="n"/>
-      <c r="S66" s="55">
+      <c r="Q66" s="169" t="n"/>
+      <c r="R66" s="169" t="n"/>
+      <c r="S66" s="173">
         <f>G66*$Q$3</f>
         <v/>
       </c>
-      <c r="T66" s="55">
+      <c r="T66" s="173">
         <f>H66*$Q$3</f>
         <v/>
       </c>
-      <c r="U66" s="55">
+      <c r="U66" s="173">
         <f>I66*$Q$3</f>
         <v/>
       </c>
-      <c r="V66" s="55">
+      <c r="V66" s="173">
         <f>J66*$Q$3</f>
         <v/>
       </c>
-      <c r="W66" s="55">
+      <c r="W66" s="173">
         <f>K66*$Q$3</f>
         <v/>
       </c>
-      <c r="X66" s="55">
+      <c r="X66" s="173">
         <f>L66*$Q$3</f>
         <v/>
       </c>
@@ -4993,48 +5368,48 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="40">
-      <c r="D67" s="51" t="inlineStr">
+      <c r="D67" s="168" t="inlineStr">
         <is>
           <t>Stemphylium</t>
         </is>
       </c>
-      <c r="E67" s="46" t="n"/>
-      <c r="F67" s="47" t="n"/>
-      <c r="G67" s="53" t="n"/>
-      <c r="H67" s="53" t="n"/>
-      <c r="I67" s="53" t="n"/>
-      <c r="J67" s="53" t="n"/>
-      <c r="K67" s="53" t="n"/>
-      <c r="L67" s="53" t="n"/>
-      <c r="M67" s="53" t="n"/>
-      <c r="P67" s="54" t="inlineStr">
+      <c r="E67" s="169" t="n"/>
+      <c r="F67" s="169" t="n"/>
+      <c r="G67" s="171" t="n"/>
+      <c r="H67" s="171" t="n"/>
+      <c r="I67" s="171" t="n"/>
+      <c r="J67" s="171" t="n"/>
+      <c r="K67" s="171" t="n"/>
+      <c r="L67" s="171" t="n"/>
+      <c r="M67" s="171" t="n"/>
+      <c r="P67" s="172" t="inlineStr">
         <is>
           <t>Stemphylium</t>
         </is>
       </c>
-      <c r="Q67" s="46" t="n"/>
-      <c r="R67" s="47" t="n"/>
-      <c r="S67" s="55">
+      <c r="Q67" s="169" t="n"/>
+      <c r="R67" s="169" t="n"/>
+      <c r="S67" s="173">
         <f>G67*$Q$3</f>
         <v/>
       </c>
-      <c r="T67" s="55">
+      <c r="T67" s="173">
         <f>H67*$Q$3</f>
         <v/>
       </c>
-      <c r="U67" s="55">
+      <c r="U67" s="173">
         <f>I67*$Q$3</f>
         <v/>
       </c>
-      <c r="V67" s="55">
+      <c r="V67" s="173">
         <f>J67*$Q$3</f>
         <v/>
       </c>
-      <c r="W67" s="55">
+      <c r="W67" s="173">
         <f>K67*$Q$3</f>
         <v/>
       </c>
-      <c r="X67" s="55">
+      <c r="X67" s="173">
         <f>L67*$Q$3</f>
         <v/>
       </c>
@@ -5048,48 +5423,48 @@
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="40">
-      <c r="D68" s="51" t="inlineStr">
+      <c r="D68" s="168" t="inlineStr">
         <is>
           <t>Tetraploa</t>
         </is>
       </c>
-      <c r="E68" s="46" t="n"/>
-      <c r="F68" s="47" t="n"/>
-      <c r="G68" s="53" t="n"/>
-      <c r="H68" s="53" t="n"/>
-      <c r="I68" s="53" t="n"/>
-      <c r="J68" s="53" t="n"/>
-      <c r="K68" s="53" t="n"/>
-      <c r="L68" s="53" t="n"/>
-      <c r="M68" s="53" t="n"/>
-      <c r="P68" s="54" t="inlineStr">
+      <c r="E68" s="169" t="n"/>
+      <c r="F68" s="169" t="n"/>
+      <c r="G68" s="171" t="n"/>
+      <c r="H68" s="171" t="n"/>
+      <c r="I68" s="171" t="n"/>
+      <c r="J68" s="171" t="n"/>
+      <c r="K68" s="171" t="n"/>
+      <c r="L68" s="171" t="n"/>
+      <c r="M68" s="171" t="n"/>
+      <c r="P68" s="172" t="inlineStr">
         <is>
           <t>Tetraploa</t>
         </is>
       </c>
-      <c r="Q68" s="46" t="n"/>
-      <c r="R68" s="47" t="n"/>
-      <c r="S68" s="55">
+      <c r="Q68" s="169" t="n"/>
+      <c r="R68" s="169" t="n"/>
+      <c r="S68" s="173">
         <f>G68*$Q$3</f>
         <v/>
       </c>
-      <c r="T68" s="55">
+      <c r="T68" s="173">
         <f>H68*$Q$3</f>
         <v/>
       </c>
-      <c r="U68" s="55">
+      <c r="U68" s="173">
         <f>I68*$Q$3</f>
         <v/>
       </c>
-      <c r="V68" s="55">
+      <c r="V68" s="173">
         <f>J68*$Q$3</f>
         <v/>
       </c>
-      <c r="W68" s="55">
+      <c r="W68" s="173">
         <f>K68*$Q$3</f>
         <v/>
       </c>
-      <c r="X68" s="55">
+      <c r="X68" s="173">
         <f>L68*$Q$3</f>
         <v/>
       </c>
@@ -5103,48 +5478,48 @@
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="40">
-      <c r="D69" s="51" t="inlineStr">
+      <c r="D69" s="168" t="inlineStr">
         <is>
           <t>Torula</t>
         </is>
       </c>
-      <c r="E69" s="46" t="n"/>
-      <c r="F69" s="47" t="n"/>
-      <c r="G69" s="53" t="n"/>
-      <c r="H69" s="53" t="n"/>
-      <c r="I69" s="53" t="n"/>
-      <c r="J69" s="53" t="n"/>
-      <c r="K69" s="53" t="n"/>
-      <c r="L69" s="53" t="n"/>
-      <c r="M69" s="53" t="n"/>
-      <c r="P69" s="54" t="inlineStr">
+      <c r="E69" s="169" t="n"/>
+      <c r="F69" s="169" t="n"/>
+      <c r="G69" s="171" t="n"/>
+      <c r="H69" s="171" t="n"/>
+      <c r="I69" s="171" t="n"/>
+      <c r="J69" s="171" t="n"/>
+      <c r="K69" s="171" t="n"/>
+      <c r="L69" s="171" t="n"/>
+      <c r="M69" s="171" t="n"/>
+      <c r="P69" s="172" t="inlineStr">
         <is>
           <t>Torula</t>
         </is>
       </c>
-      <c r="Q69" s="46" t="n"/>
-      <c r="R69" s="47" t="n"/>
-      <c r="S69" s="55">
+      <c r="Q69" s="169" t="n"/>
+      <c r="R69" s="169" t="n"/>
+      <c r="S69" s="173">
         <f>G69*$Q$3</f>
         <v/>
       </c>
-      <c r="T69" s="55">
+      <c r="T69" s="173">
         <f>H69*$Q$3</f>
         <v/>
       </c>
-      <c r="U69" s="55">
+      <c r="U69" s="173">
         <f>I69*$Q$3</f>
         <v/>
       </c>
-      <c r="V69" s="55">
+      <c r="V69" s="173">
         <f>J69*$Q$3</f>
         <v/>
       </c>
-      <c r="W69" s="55">
+      <c r="W69" s="173">
         <f>K69*$Q$3</f>
         <v/>
       </c>
-      <c r="X69" s="55">
+      <c r="X69" s="173">
         <f>L69*$Q$3</f>
         <v/>
       </c>
@@ -5158,69 +5533,69 @@
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="40">
-      <c r="D70" s="58" t="inlineStr">
+      <c r="D70" s="174" t="inlineStr">
         <is>
           <t>Totali</t>
         </is>
       </c>
-      <c r="E70" s="46" t="n"/>
-      <c r="F70" s="47" t="n"/>
-      <c r="G70" s="58">
+      <c r="E70" s="166" t="n"/>
+      <c r="F70" s="166" t="n"/>
+      <c r="G70" s="174">
         <f>SUM(G58:G69)</f>
         <v/>
       </c>
-      <c r="H70" s="58">
+      <c r="H70" s="174">
         <f>SUM(H58:H69)</f>
         <v/>
       </c>
-      <c r="I70" s="58">
+      <c r="I70" s="174">
         <f>SUM(I58:I69)</f>
         <v/>
       </c>
-      <c r="J70" s="58">
+      <c r="J70" s="174">
         <f>SUM(J58:J69)</f>
         <v/>
       </c>
-      <c r="K70" s="58">
+      <c r="K70" s="174">
         <f>SUM(K58:K69)</f>
         <v/>
       </c>
-      <c r="L70" s="58">
+      <c r="L70" s="174">
         <f>SUM(L58:L69)</f>
         <v/>
       </c>
-      <c r="M70" s="58">
+      <c r="M70" s="174">
         <f>SUM(M58:M69)</f>
         <v/>
       </c>
-      <c r="P70" s="58" t="inlineStr">
+      <c r="P70" s="174" t="inlineStr">
         <is>
           <t>Totali</t>
         </is>
       </c>
-      <c r="Q70" s="46" t="n"/>
-      <c r="R70" s="47" t="n"/>
-      <c r="S70" s="58">
+      <c r="Q70" s="166" t="n"/>
+      <c r="R70" s="166" t="n"/>
+      <c r="S70" s="174">
         <f>SUM(S58:S69)</f>
         <v/>
       </c>
-      <c r="T70" s="58">
+      <c r="T70" s="174">
         <f>SUM(T58:T69)</f>
         <v/>
       </c>
-      <c r="U70" s="58">
+      <c r="U70" s="174">
         <f>SUM(U58:U69)</f>
         <v/>
       </c>
-      <c r="V70" s="58">
+      <c r="V70" s="174">
         <f>SUM(V58:V69)</f>
         <v/>
       </c>
-      <c r="W70" s="58">
+      <c r="W70" s="174">
         <f>SUM(W58:W69)</f>
         <v/>
       </c>
-      <c r="X70" s="58">
+      <c r="X70" s="174">
         <f>SUM(X58:X69)</f>
         <v/>
       </c>
@@ -5481,35 +5856,35 @@
         </is>
       </c>
       <c r="E77" s="80">
-        <f>IF(G8&gt;0,ROUND(G8*$Q$3,1),0)</f>
+        <f>IF((G8+G9+G10)&gt;0,ROUND((G8+G9+G10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F77" s="80">
-        <f>IF(H8&gt;0,ROUND(H8*$Q$3,1),0)</f>
+        <f>IF((H8+H9+H10)&gt;0,ROUND((H8+H9+H10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G77" s="80">
-        <f>IF(I8&gt;0,ROUND(I8*$Q$3,1),0)</f>
+        <f>IF((I8+I9+I10)&gt;0,ROUND((I8+I9+I10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H77" s="80">
-        <f>IF(J8&gt;0,ROUND(J8*$Q$3,1),0)</f>
+        <f>IF((J8+J9+J10)&gt;0,ROUND((J8+J9+J10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I77" s="80">
-        <f>IF(K8&gt;0,ROUND(K8*$Q$3,1),0)</f>
+        <f>IF((K8+K9+K10)&gt;0,ROUND((K8+K9+K10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J77" s="80">
-        <f>IF(L8&gt;0,ROUND(L8*$Q$3,1),0)</f>
+        <f>IF((L8+L9+L10)&gt;0,ROUND((L8+L9+L10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K77" s="80">
-        <f>IF(M8&gt;0,ROUND(M8*$Q$3,1),0)</f>
+        <f>IF((M8+M9+M10)&gt;0,ROUND((M8+M9+M10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L77" s="80">
-        <f>ROUND(SUM(G8:M8)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G8:M8)+SUM(G9:M9)+SUM(G10:M10))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M77" s="76" t="n"/>
@@ -5521,35 +5896,35 @@
         </is>
       </c>
       <c r="Q77" s="80">
-        <f>IF(G8&gt;0,ROUND(G8*$Q$3,1),0)</f>
+        <f>IF((G8+G9+G10)&gt;0,ROUND((G8+G9+G10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R77" s="80">
-        <f>IF(H8&gt;0,ROUND(H8*$Q$3,1),0)</f>
+        <f>IF((H8+H9+H10)&gt;0,ROUND((H8+H9+H10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S77" s="80">
-        <f>IF(I8&gt;0,ROUND(I8*$Q$3,1),0)</f>
+        <f>IF((I8+I9+I10)&gt;0,ROUND((I8+I9+I10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T77" s="80">
-        <f>IF(J8&gt;0,ROUND(J8*$Q$3,1),0)</f>
+        <f>IF((J8+J9+J10)&gt;0,ROUND((J8+J9+J10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U77" s="80">
-        <f>IF(K8&gt;0,ROUND(K8*$Q$3,1),0)</f>
+        <f>IF((K8+K9+K10)&gt;0,ROUND((K8+K9+K10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V77" s="80">
-        <f>IF(L8&gt;0,ROUND(L8*$Q$3,1),0)</f>
+        <f>IF((L8+L9+L10)&gt;0,ROUND((L8+L9+L10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W77" s="80">
-        <f>IF(M8&gt;0,ROUND(M8*$Q$3,1),0)</f>
+        <f>IF((M8+M9+M10)&gt;0,ROUND((M8+M9+M10)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X77" s="80">
-        <f>ROUND(SUM(G8:M8)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G8:M8)+SUM(G9:M9)+SUM(G10:M10))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y77" s="81" t="n"/>
@@ -5801,35 +6176,35 @@
         </is>
       </c>
       <c r="E81" s="80">
-        <f>IF(G13&gt;0,ROUND(G13*$Q$3,1),0)</f>
+        <f>IF((G13+G14+G15+G16)&gt;0,ROUND((G13+G14+G15+G16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F81" s="80">
-        <f>IF(H13&gt;0,ROUND(H13*$Q$3,1),0)</f>
+        <f>IF((H13+H14+H15+H16)&gt;0,ROUND((H13+H14+H15+H16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G81" s="80">
-        <f>IF(I13&gt;0,ROUND(I13*$Q$3,1),0)</f>
+        <f>IF((I13+I14+I15+I16)&gt;0,ROUND((I13+I14+I15+I16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H81" s="80">
-        <f>IF(J13&gt;0,ROUND(J13*$Q$3,1),0)</f>
+        <f>IF((J13+J14+J15+J16)&gt;0,ROUND((J13+J14+J15+J16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I81" s="80">
-        <f>IF(K13&gt;0,ROUND(K13*$Q$3,1),0)</f>
+        <f>IF((K13+K14+K15+K16)&gt;0,ROUND((K13+K14+K15+K16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J81" s="80">
-        <f>IF(L13&gt;0,ROUND(L13*$Q$3,1),0)</f>
+        <f>IF((L13+L14+L15+L16)&gt;0,ROUND((L13+L14+L15+L16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K81" s="80">
-        <f>IF(M13&gt;0,ROUND(M13*$Q$3,1),0)</f>
+        <f>IF((M13+M14+M15+M16)&gt;0,ROUND((M13+M14+M15+M16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L81" s="80">
-        <f>ROUND(SUM(G13:M13)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G13:M13)+SUM(G14:M14)+SUM(G15:M15)+SUM(G16:M16))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M81" s="76" t="n"/>
@@ -5841,35 +6216,35 @@
         </is>
       </c>
       <c r="Q81" s="80">
-        <f>IF(G13&gt;0,ROUND(G13*$Q$3,1),0)</f>
+        <f>IF((G13+G14+G15+G16)&gt;0,ROUND((G13+G14+G15+G16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R81" s="80">
-        <f>IF(H13&gt;0,ROUND(H13*$Q$3,1),0)</f>
+        <f>IF((H13+H14+H15+H16)&gt;0,ROUND((H13+H14+H15+H16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S81" s="80">
-        <f>IF(I13&gt;0,ROUND(I13*$Q$3,1),0)</f>
+        <f>IF((I13+I14+I15+I16)&gt;0,ROUND((I13+I14+I15+I16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T81" s="80">
-        <f>IF(J13&gt;0,ROUND(J13*$Q$3,1),0)</f>
+        <f>IF((J13+J14+J15+J16)&gt;0,ROUND((J13+J14+J15+J16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U81" s="80">
-        <f>IF(K13&gt;0,ROUND(K13*$Q$3,1),0)</f>
+        <f>IF((K13+K14+K15+K16)&gt;0,ROUND((K13+K14+K15+K16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V81" s="80">
-        <f>IF(L13&gt;0,ROUND(L13*$Q$3,1),0)</f>
+        <f>IF((L13+L14+L15+L16)&gt;0,ROUND((L13+L14+L15+L16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W81" s="80">
-        <f>IF(M13&gt;0,ROUND(M13*$Q$3,1),0)</f>
+        <f>IF((M13+M14+M15+M16)&gt;0,ROUND((M13+M14+M15+M16)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X81" s="80">
-        <f>ROUND(SUM(G13:M13)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G13:M13)+SUM(G14:M14)+SUM(G15:M15)+SUM(G16:M16))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y81" s="81" t="n"/>
@@ -6121,35 +6496,35 @@
         </is>
       </c>
       <c r="E85" s="80">
-        <f>IF(G17&gt;0,ROUND(G17*$Q$3,1),0)</f>
+        <f>IF((G17+G18+G19+G20+G21)&gt;0,ROUND((G17+G18+G19+G20+G21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F85" s="80">
-        <f>IF(H17&gt;0,ROUND(H17*$Q$3,1),0)</f>
+        <f>IF((H17+H18+H19+H20+H21)&gt;0,ROUND((H17+H18+H19+H20+H21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G85" s="80">
-        <f>IF(I17&gt;0,ROUND(I17*$Q$3,1),0)</f>
+        <f>IF((I17+I18+I19+I20+I21)&gt;0,ROUND((I17+I18+I19+I20+I21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H85" s="80">
-        <f>IF(J17&gt;0,ROUND(J17*$Q$3,1),0)</f>
+        <f>IF((J17+J18+J19+J20+J21)&gt;0,ROUND((J17+J18+J19+J20+J21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I85" s="80">
-        <f>IF(K17&gt;0,ROUND(K17*$Q$3,1),0)</f>
+        <f>IF((K17+K18+K19+K20+K21)&gt;0,ROUND((K17+K18+K19+K20+K21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J85" s="80">
-        <f>IF(L17&gt;0,ROUND(L17*$Q$3,1),0)</f>
+        <f>IF((L17+L18+L19+L20+L21)&gt;0,ROUND((L17+L18+L19+L20+L21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K85" s="80">
-        <f>IF(M17&gt;0,ROUND(M17*$Q$3,1),0)</f>
+        <f>IF((M17+M18+M19+M20+M21)&gt;0,ROUND((M17+M18+M19+M20+M21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L85" s="80">
-        <f>ROUND(SUM(G17:M17)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G17:M17)+SUM(G18:M18)+SUM(G19:M19)+SUM(G20:M20)+SUM(G21:M21))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M85" s="76" t="n"/>
@@ -6161,35 +6536,35 @@
         </is>
       </c>
       <c r="Q85" s="80">
-        <f>IF(G17&gt;0,ROUND(G17*$Q$3,1),0)</f>
+        <f>IF((G17+G18+G19+G20+G21)&gt;0,ROUND((G17+G18+G19+G20+G21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R85" s="80">
-        <f>IF(H17&gt;0,ROUND(H17*$Q$3,1),0)</f>
+        <f>IF((H17+H18+H19+H20+H21)&gt;0,ROUND((H17+H18+H19+H20+H21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S85" s="80">
-        <f>IF(I17&gt;0,ROUND(I17*$Q$3,1),0)</f>
+        <f>IF((I17+I18+I19+I20+I21)&gt;0,ROUND((I17+I18+I19+I20+I21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T85" s="80">
-        <f>IF(J17&gt;0,ROUND(J17*$Q$3,1),0)</f>
+        <f>IF((J17+J18+J19+J20+J21)&gt;0,ROUND((J17+J18+J19+J20+J21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U85" s="80">
-        <f>IF(K17&gt;0,ROUND(K17*$Q$3,1),0)</f>
+        <f>IF((K17+K18+K19+K20+K21)&gt;0,ROUND((K17+K18+K19+K20+K21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V85" s="80">
-        <f>IF(L17&gt;0,ROUND(L17*$Q$3,1),0)</f>
+        <f>IF((L17+L18+L19+L20+L21)&gt;0,ROUND((L17+L18+L19+L20+L21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W85" s="80">
-        <f>IF(M17&gt;0,ROUND(M17*$Q$3,1),0)</f>
+        <f>IF((M17+M18+M19+M20+M21)&gt;0,ROUND((M17+M18+M19+M20+M21)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X85" s="80">
-        <f>ROUND(SUM(G17:M17)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G17:M17)+SUM(G18:M18)+SUM(G19:M19)+SUM(G20:M20)+SUM(G21:M21))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y85" s="81" t="n"/>
@@ -6601,35 +6976,35 @@
         </is>
       </c>
       <c r="E91" s="80">
-        <f>IF(G25&gt;0,ROUND(G25*$Q$3,1),0)</f>
+        <f>IF((G25+G26+G27+G28)&gt;0,ROUND((G25+G26+G27+G28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F91" s="80">
-        <f>IF(H25&gt;0,ROUND(H25*$Q$3,1),0)</f>
+        <f>IF((H25+H26+H27+H28)&gt;0,ROUND((H25+H26+H27+H28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G91" s="80">
-        <f>IF(I25&gt;0,ROUND(I25*$Q$3,1),0)</f>
+        <f>IF((I25+I26+I27+I28)&gt;0,ROUND((I25+I26+I27+I28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H91" s="80">
-        <f>IF(J25&gt;0,ROUND(J25*$Q$3,1),0)</f>
+        <f>IF((J25+J26+J27+J28)&gt;0,ROUND((J25+J26+J27+J28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I91" s="80">
-        <f>IF(K25&gt;0,ROUND(K25*$Q$3,1),0)</f>
+        <f>IF((K25+K26+K27+K28)&gt;0,ROUND((K25+K26+K27+K28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J91" s="80">
-        <f>IF(L25&gt;0,ROUND(L25*$Q$3,1),0)</f>
+        <f>IF((L25+L26+L27+L28)&gt;0,ROUND((L25+L26+L27+L28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K91" s="80">
-        <f>IF(M25&gt;0,ROUND(M25*$Q$3,1),0)</f>
+        <f>IF((M25+M26+M27+M28)&gt;0,ROUND((M25+M26+M27+M28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L91" s="80">
-        <f>ROUND(SUM(G25:M25)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G25:M25)+SUM(G26:M26)+SUM(G27:M27)+SUM(G28:M28))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M91" s="76" t="n"/>
@@ -6641,35 +7016,35 @@
         </is>
       </c>
       <c r="Q91" s="80">
-        <f>IF(G25&gt;0,ROUND(G25*$Q$3,1),0)</f>
+        <f>IF((G25+G26+G27+G28)&gt;0,ROUND((G25+G26+G27+G28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R91" s="80">
-        <f>IF(H25&gt;0,ROUND(H25*$Q$3,1),0)</f>
+        <f>IF((H25+H26+H27+H28)&gt;0,ROUND((H25+H26+H27+H28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S91" s="80">
-        <f>IF(I25&gt;0,ROUND(I25*$Q$3,1),0)</f>
+        <f>IF((I25+I26+I27+I28)&gt;0,ROUND((I25+I26+I27+I28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T91" s="80">
-        <f>IF(J25&gt;0,ROUND(J25*$Q$3,1),0)</f>
+        <f>IF((J25+J26+J27+J28)&gt;0,ROUND((J25+J26+J27+J28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U91" s="80">
-        <f>IF(K25&gt;0,ROUND(K25*$Q$3,1),0)</f>
+        <f>IF((K25+K26+K27+K28)&gt;0,ROUND((K25+K26+K27+K28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V91" s="80">
-        <f>IF(L25&gt;0,ROUND(L25*$Q$3,1),0)</f>
+        <f>IF((L25+L26+L27+L28)&gt;0,ROUND((L25+L26+L27+L28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W91" s="80">
-        <f>IF(M25&gt;0,ROUND(M25*$Q$3,1),0)</f>
+        <f>IF((M25+M26+M27+M28)&gt;0,ROUND((M25+M26+M27+M28)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X91" s="80">
-        <f>ROUND(SUM(G25:M25)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G25:M25)+SUM(G26:M26)+SUM(G27:M27)+SUM(G28:M28))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y91" s="81" t="n"/>
@@ -7001,35 +7376,35 @@
         </is>
       </c>
       <c r="E96" s="80">
-        <f>IF(G36&gt;0,ROUND(G36*$Q$3,1),0)</f>
+        <f>IF((G36+G37+G38+G39+G40)&gt;0,ROUND((G36+G37+G38+G39+G40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F96" s="80">
-        <f>IF(H36&gt;0,ROUND(H36*$Q$3,1),0)</f>
+        <f>IF((H36+H37+H38+H39+H40)&gt;0,ROUND((H36+H37+H38+H39+H40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G96" s="80">
-        <f>IF(I36&gt;0,ROUND(I36*$Q$3,1),0)</f>
+        <f>IF((I36+I37+I38+I39+I40)&gt;0,ROUND((I36+I37+I38+I39+I40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H96" s="80">
-        <f>IF(J36&gt;0,ROUND(J36*$Q$3,1),0)</f>
+        <f>IF((J36+J37+J38+J39+J40)&gt;0,ROUND((J36+J37+J38+J39+J40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I96" s="80">
-        <f>IF(K36&gt;0,ROUND(K36*$Q$3,1),0)</f>
+        <f>IF((K36+K37+K38+K39+K40)&gt;0,ROUND((K36+K37+K38+K39+K40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J96" s="80">
-        <f>IF(L36&gt;0,ROUND(L36*$Q$3,1),0)</f>
+        <f>IF((L36+L37+L38+L39+L40)&gt;0,ROUND((L36+L37+L38+L39+L40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K96" s="80">
-        <f>IF(M36&gt;0,ROUND(M36*$Q$3,1),0)</f>
+        <f>IF((M36+M37+M38+M39+M40)&gt;0,ROUND((M36+M37+M38+M39+M40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L96" s="80">
-        <f>ROUND(SUM(G36:M36)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G36:M36)+SUM(G37:M37)+SUM(G38:M38)+SUM(G39:M39)+SUM(G40:M40))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M96" s="76" t="n"/>
@@ -7041,35 +7416,35 @@
         </is>
       </c>
       <c r="Q96" s="80">
-        <f>IF(G36&gt;0,ROUND(G36*$Q$3,1),0)</f>
+        <f>IF((G36+G37+G38+G39+G40)&gt;0,ROUND((G36+G37+G38+G39+G40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R96" s="80">
-        <f>IF(H36&gt;0,ROUND(H36*$Q$3,1),0)</f>
+        <f>IF((H36+H37+H38+H39+H40)&gt;0,ROUND((H36+H37+H38+H39+H40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S96" s="80">
-        <f>IF(I36&gt;0,ROUND(I36*$Q$3,1),0)</f>
+        <f>IF((I36+I37+I38+I39+I40)&gt;0,ROUND((I36+I37+I38+I39+I40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T96" s="80">
-        <f>IF(J36&gt;0,ROUND(J36*$Q$3,1),0)</f>
+        <f>IF((J36+J37+J38+J39+J40)&gt;0,ROUND((J36+J37+J38+J39+J40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U96" s="80">
-        <f>IF(K36&gt;0,ROUND(K36*$Q$3,1),0)</f>
+        <f>IF((K36+K37+K38+K39+K40)&gt;0,ROUND((K36+K37+K38+K39+K40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V96" s="80">
-        <f>IF(L36&gt;0,ROUND(L36*$Q$3,1),0)</f>
+        <f>IF((L36+L37+L38+L39+L40)&gt;0,ROUND((L36+L37+L38+L39+L40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W96" s="80">
-        <f>IF(M36&gt;0,ROUND(M36*$Q$3,1),0)</f>
+        <f>IF((M36+M37+M38+M39+M40)&gt;0,ROUND((M36+M37+M38+M39+M40)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X96" s="80">
-        <f>ROUND(SUM(G36:M36)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G36:M36)+SUM(G37:M37)+SUM(G38:M38)+SUM(G39:M39)+SUM(G40:M40))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y96" s="81" t="n"/>
@@ -7641,35 +8016,35 @@
         </is>
       </c>
       <c r="E104" s="80">
-        <f>IF(G46&gt;0,ROUND(G46*$Q$3,1),0)</f>
+        <f>IF((G46+G47+G48)&gt;0,ROUND((G46+G47+G48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="F104" s="80">
-        <f>IF(H46&gt;0,ROUND(H46*$Q$3,1),0)</f>
+        <f>IF((H46+H47+H48)&gt;0,ROUND((H46+H47+H48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="G104" s="80">
-        <f>IF(I46&gt;0,ROUND(I46*$Q$3,1),0)</f>
+        <f>IF((I46+I47+I48)&gt;0,ROUND((I46+I47+I48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="H104" s="80">
-        <f>IF(J46&gt;0,ROUND(J46*$Q$3,1),0)</f>
+        <f>IF((J46+J47+J48)&gt;0,ROUND((J46+J47+J48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="I104" s="80">
-        <f>IF(K46&gt;0,ROUND(K46*$Q$3,1),0)</f>
+        <f>IF((K46+K47+K48)&gt;0,ROUND((K46+K47+K48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="J104" s="80">
-        <f>IF(L46&gt;0,ROUND(L46*$Q$3,1),0)</f>
+        <f>IF((L46+L47+L48)&gt;0,ROUND((L46+L47+L48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="K104" s="80">
-        <f>IF(M46&gt;0,ROUND(M46*$Q$3,1),0)</f>
+        <f>IF((M46+M47+M48)&gt;0,ROUND((M46+M47+M48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="L104" s="80">
-        <f>ROUND(SUM(G46:M46)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G46:M46)+SUM(G47:M47)+SUM(G48:M48))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="M104" s="76" t="n"/>
@@ -7681,35 +8056,35 @@
         </is>
       </c>
       <c r="Q104" s="80">
-        <f>IF(G46&gt;0,ROUND(G46*$Q$3,1),0)</f>
+        <f>IF((G46+G47+G48)&gt;0,ROUND((G46+G47+G48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="R104" s="80">
-        <f>IF(H46&gt;0,ROUND(H46*$Q$3,1),0)</f>
+        <f>IF((H46+H47+H48)&gt;0,ROUND((H46+H47+H48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="S104" s="80">
-        <f>IF(I46&gt;0,ROUND(I46*$Q$3,1),0)</f>
+        <f>IF((I46+I47+I48)&gt;0,ROUND((I46+I47+I48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="T104" s="80">
-        <f>IF(J46&gt;0,ROUND(J46*$Q$3,1),0)</f>
+        <f>IF((J46+J47+J48)&gt;0,ROUND((J46+J47+J48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="U104" s="80">
-        <f>IF(K46&gt;0,ROUND(K46*$Q$3,1),0)</f>
+        <f>IF((K46+K47+K48)&gt;0,ROUND((K46+K47+K48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="V104" s="80">
-        <f>IF(L46&gt;0,ROUND(L46*$Q$3,1),0)</f>
+        <f>IF((L46+L47+L48)&gt;0,ROUND((L46+L47+L48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="W104" s="80">
-        <f>IF(M46&gt;0,ROUND(M46*$Q$3,1),0)</f>
+        <f>IF((M46+M47+M48)&gt;0,ROUND((M46+M47+M48)*$Q$3,1),0)</f>
         <v/>
       </c>
       <c r="X104" s="80">
-        <f>ROUND(SUM(G46:M46)*$Q$3/7,1)</f>
+        <f>ROUND((SUM(G46:M46)+SUM(G47:M47)+SUM(G48:M48))*$Q$3/7,1)</f>
         <v/>
       </c>
       <c r="Y104" s="81" t="n"/>
@@ -8583,494 +8958,984 @@
     <mergeCell ref="P34:R34"/>
     <mergeCell ref="D49:F49"/>
   </mergeCells>
+  <conditionalFormatting sqref="E76:L76">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Q76:X76">
-    <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>19.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E77:L77">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q77:X77">
-    <cfRule type="cellIs" priority="5" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="16" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E78:L78">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q78:X78">
-    <cfRule type="cellIs" priority="9" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="21" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="24" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79:L79">
+    <cfRule type="cellIs" priority="25" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="27" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q79:X79">
-    <cfRule type="cellIs" priority="13" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="29" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>15.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="32" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E80:L80">
+    <cfRule type="cellIs" priority="33" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:X80">
-    <cfRule type="cellIs" priority="17" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="37" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="39" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="40" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E81:L81">
+    <cfRule type="cellIs" priority="41" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="20" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="43" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q81:X81">
-    <cfRule type="cellIs" priority="21" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="45" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="47" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="22" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="48" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E82:L82">
+    <cfRule type="cellIs" priority="49" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="50" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="23" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="24" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="51" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q82:X82">
-    <cfRule type="cellIs" priority="25" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="53" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="55" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="56" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E83:L83">
+    <cfRule type="cellIs" priority="57" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="58" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="27" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="28" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="59" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="60" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83:X83">
-    <cfRule type="cellIs" priority="29" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="61" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="62" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="63" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="64" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E84:L84">
+    <cfRule type="cellIs" priority="65" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="66" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="32" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="67" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="68" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q84:X84">
-    <cfRule type="cellIs" priority="33" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="69" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="70" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="71" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>4.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="35" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="36" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="72" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E85:L85">
+    <cfRule type="cellIs" priority="73" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="74" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="75" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="76" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q85:X85">
-    <cfRule type="cellIs" priority="37" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="77" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="78" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="79" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="80" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E86:L86">
+    <cfRule type="cellIs" priority="81" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="82" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="40" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="83" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="84" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q86:X86">
-    <cfRule type="cellIs" priority="41" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="85" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="86" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="87" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="42" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="88" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E87:L87">
+    <cfRule type="cellIs" priority="89" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="90" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="43" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="44" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="91" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="92" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q87:X87">
-    <cfRule type="cellIs" priority="45" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="93" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="94" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="95" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="46" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="96" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E88:L88">
+    <cfRule type="cellIs" priority="97" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="98" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="47" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="48" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="99" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="100" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q88:X88">
-    <cfRule type="cellIs" priority="49" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="101" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="102" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="103" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="50" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="104" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E89:L89">
+    <cfRule type="cellIs" priority="105" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="106" operator="greaterThan" dxfId="4">
       <formula>15.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="51" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="52" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="107" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="108" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q89:X89">
-    <cfRule type="cellIs" priority="53" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="109" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="110" operator="greaterThan" dxfId="4">
+      <formula>15.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="111" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="54" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>15.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="55" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="56" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="112" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E90:L90">
+    <cfRule type="cellIs" priority="113" operator="greaterThan" dxfId="3">
+      <formula>89.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="114" operator="greaterThan" dxfId="4">
+      <formula>29.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="115" operator="greaterThan" dxfId="5">
+      <formula>3.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="116" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q90:X90">
-    <cfRule type="cellIs" priority="57" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="117" operator="greaterThan" dxfId="3">
+      <formula>89.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="118" operator="greaterThan" dxfId="4">
+      <formula>29.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="119" operator="greaterThan" dxfId="5">
       <formula>3.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="58" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>29.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="59" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>89.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="60" operator="greaterThan" dxfId="3">
-      <formula>89.9</formula>
+    <cfRule type="cellIs" priority="120" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E91:L91">
+    <cfRule type="cellIs" priority="121" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="122" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="123" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="124" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q91:X91">
-    <cfRule type="cellIs" priority="61" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="125" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="126" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="127" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="62" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="128" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E92:L92">
+    <cfRule type="cellIs" priority="129" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="130" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="63" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="64" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="131" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="132" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q92:X92">
-    <cfRule type="cellIs" priority="65" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="133" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="134" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="135" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="136" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E93:L93">
+    <cfRule type="cellIs" priority="137" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="138" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="67" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="68" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="139" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="140" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q93:X93">
-    <cfRule type="cellIs" priority="69" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="141" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="142" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="143" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="70" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="144" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E94:L94">
+    <cfRule type="cellIs" priority="145" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="146" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="71" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="72" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="147" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="148" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q94:X94">
-    <cfRule type="cellIs" priority="73" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="149" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="150" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="151" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="74" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>19.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="75" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="76" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="152" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E95:L95">
+    <cfRule type="cellIs" priority="153" operator="greaterThan" dxfId="3">
+      <formula>29.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="154" operator="greaterThan" dxfId="4">
+      <formula>9.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="155" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="156" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q95:X95">
-    <cfRule type="cellIs" priority="77" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="157" operator="greaterThan" dxfId="3">
+      <formula>29.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="158" operator="greaterThan" dxfId="4">
+      <formula>9.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="159" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="78" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>9.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="79" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>29.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="80" operator="greaterThan" dxfId="3">
-      <formula>29.9</formula>
+    <cfRule type="cellIs" priority="160" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E96:L96">
+    <cfRule type="cellIs" priority="161" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="162" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="163" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="164" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q96:X96">
-    <cfRule type="cellIs" priority="81" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="165" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="166" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="167" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="82" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="168" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E97:L97">
+    <cfRule type="cellIs" priority="169" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="170" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="83" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="84" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="171" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="172" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:X97">
-    <cfRule type="cellIs" priority="85" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="173" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="174" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="175" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="86" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="176" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E98:L98">
+    <cfRule type="cellIs" priority="177" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="178" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="87" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="88" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="179" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="180" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q98:X98">
-    <cfRule type="cellIs" priority="89" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="181" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="182" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="183" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="90" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="184" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E99:L99">
+    <cfRule type="cellIs" priority="185" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="186" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="91" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="92" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="187" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="188" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q99:X99">
-    <cfRule type="cellIs" priority="93" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="189" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="190" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="191" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="94" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="192" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E100:L100">
+    <cfRule type="cellIs" priority="193" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="194" operator="greaterThan" dxfId="4">
       <formula>4.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="95" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="96" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="195" operator="greaterThan" dxfId="5">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="196" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q100:X100">
-    <cfRule type="cellIs" priority="97" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="197" operator="greaterThan" dxfId="3">
+      <formula>24.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="198" operator="greaterThan" dxfId="4">
+      <formula>4.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="199" operator="greaterThan" dxfId="5">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="98" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>4.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="99" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>24.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="100" operator="greaterThan" dxfId="3">
-      <formula>24.9</formula>
+    <cfRule type="cellIs" priority="200" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E101:L101">
+    <cfRule type="cellIs" priority="201" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="202" operator="greaterThan" dxfId="4">
+      <formula>14.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="203" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="204" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:X101">
-    <cfRule type="cellIs" priority="101" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="205" operator="greaterThan" dxfId="3">
+      <formula>49.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="206" operator="greaterThan" dxfId="4">
+      <formula>14.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="207" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="102" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>14.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="103" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>49.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="104" operator="greaterThan" dxfId="3">
-      <formula>49.9</formula>
+    <cfRule type="cellIs" priority="208" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E102:L102">
+    <cfRule type="cellIs" priority="209" operator="greaterThan" dxfId="3">
+      <formula>1.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="210" operator="greaterThan" dxfId="4">
+      <formula>0.4</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="211" operator="greaterThan" dxfId="5">
+      <formula>0.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="212" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:X102">
-    <cfRule type="cellIs" priority="105" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="213" operator="greaterThan" dxfId="3">
+      <formula>1.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="214" operator="greaterThan" dxfId="4">
+      <formula>0.4</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="215" operator="greaterThan" dxfId="5">
       <formula>0.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="106" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>0.4</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="107" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>1.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="108" operator="greaterThan" dxfId="3">
-      <formula>1.9</formula>
+    <cfRule type="cellIs" priority="216" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E103:L103">
+    <cfRule type="cellIs" priority="217" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="218" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="219" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="220" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:X103">
-    <cfRule type="cellIs" priority="109" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="221" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="222" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="223" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="110" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="224" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E104:L104">
+    <cfRule type="cellIs" priority="225" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="226" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="111" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="112" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="227" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="228" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q104:X104">
-    <cfRule type="cellIs" priority="113" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="229" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="230" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="231" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="114" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="232" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E105:L105">
+    <cfRule type="cellIs" priority="233" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="234" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="115" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="116" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="235" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="236" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q105:X105">
-    <cfRule type="cellIs" priority="117" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="237" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="238" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="239" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="118" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="240" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E106:L106">
+    <cfRule type="cellIs" priority="241" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="242" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="119" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="120" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="243" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="244" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q106:X106">
-    <cfRule type="cellIs" priority="121" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="245" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="246" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="247" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="122" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="248" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E107:L107">
+    <cfRule type="cellIs" priority="249" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="250" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="123" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="124" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="251" operator="greaterThan" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="252" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q107:X107">
-    <cfRule type="cellIs" priority="125" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="253" operator="greaterThan" dxfId="3">
+      <formula>39.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="254" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="255" operator="greaterThan" dxfId="5">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="126" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="256" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E108:L108">
+    <cfRule type="cellIs" priority="257" operator="greaterThan" dxfId="3">
+      <formula>69.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="258" operator="greaterThan" dxfId="4">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="127" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>39.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="128" operator="greaterThan" dxfId="3">
-      <formula>39.9</formula>
+    <cfRule type="cellIs" priority="259" operator="greaterThan" dxfId="5">
+      <formula>1.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="260" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q108:X108">
-    <cfRule type="cellIs" priority="129" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="261" operator="greaterThan" dxfId="3">
+      <formula>69.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="262" operator="greaterThan" dxfId="4">
+      <formula>19.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="263" operator="greaterThan" dxfId="5">
       <formula>1.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="130" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>19.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="131" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>69.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="132" operator="greaterThan" dxfId="3">
-      <formula>69.9</formula>
+    <cfRule type="cellIs" priority="264" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E109:L109">
+    <cfRule type="cellIs" priority="265" operator="greaterThan" dxfId="3">
+      <formula>100.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="266" operator="greaterThan" dxfId="4">
+      <formula>19.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="267" operator="greaterThan" dxfId="5">
+      <formula>1.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="268" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q109:X109">
-    <cfRule type="cellIs" priority="133" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="269" operator="greaterThan" dxfId="3">
+      <formula>100.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="270" operator="greaterThan" dxfId="4">
+      <formula>19.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="271" operator="greaterThan" dxfId="5">
       <formula>1.9</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="134" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
-      <formula>19.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="135" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="272" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E110:L110">
+    <cfRule type="cellIs" priority="273" operator="greaterThan" dxfId="3">
+      <formula>1000.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="274" operator="greaterThan" dxfId="4">
+      <formula>499.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="275" operator="greaterThan" dxfId="5">
       <formula>100.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="136" operator="greaterThan" dxfId="3">
-      <formula>100.0</formula>
+    <cfRule type="cellIs" priority="276" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q110:X110">
-    <cfRule type="cellIs" priority="137" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
-      <formula>99.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="138" operator="lessThanOrEqual" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="277" operator="greaterThan" dxfId="3">
+      <formula>1000.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="278" operator="greaterThan" dxfId="4">
       <formula>499.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="139" operator="lessThanOrEqual" dxfId="2" stopIfTrue="1">
-      <formula>1000.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="140" operator="greaterThan" dxfId="3">
-      <formula>1000.0</formula>
+    <cfRule type="cellIs" priority="279" operator="greaterThan" dxfId="5">
+      <formula>100.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="280" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
